--- a/database/event/8042/event_8042_evp_summary.xlsx
+++ b/database/event/8042/event_8042_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>9.718500000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>6.2555</v>
       </c>
       <c r="D2" t="n">
         <v>3.5047</v>
@@ -545,7 +545,7 @@
         <v>9.4213</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>6.0642</v>
       </c>
       <c r="D3" t="n">
         <v>3.3846</v>
@@ -591,7 +591,7 @@
         <v>7.3255</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4.7152</v>
       </c>
       <c r="D4" t="n">
         <v>2.538</v>
@@ -637,7 +637,7 @@
         <v>7.0202</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4.5187</v>
       </c>
       <c r="D5" t="n">
         <v>2.4146</v>
@@ -683,7 +683,7 @@
         <v>6.6647</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4.2898</v>
       </c>
       <c r="D6" t="n">
         <v>2.271</v>
@@ -729,7 +729,7 @@
         <v>5.7334</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3.6904</v>
       </c>
       <c r="D7" t="n">
         <v>1.8948</v>
@@ -775,7 +775,7 @@
         <v>5.5229</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3.5549</v>
       </c>
       <c r="D8" t="n">
         <v>1.8098</v>
@@ -821,7 +821,7 @@
         <v>5.3683</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3.4554</v>
       </c>
       <c r="D9" t="n">
         <v>1.7473</v>
@@ -867,7 +867,7 @@
         <v>5.1873</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>3.3389</v>
       </c>
       <c r="D10" t="n">
         <v>1.6742</v>
@@ -913,7 +913,7 @@
         <v>4.739</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>3.0503</v>
       </c>
       <c r="D11" t="n">
         <v>1.4931</v>
@@ -959,7 +959,7 @@
         <v>4.2215</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2.7172</v>
       </c>
       <c r="D12" t="n">
         <v>1.284</v>
@@ -1005,7 +1005,7 @@
         <v>4.0797</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2.626</v>
       </c>
       <c r="D13" t="n">
         <v>1.2267</v>
@@ -1051,7 +1051,7 @@
         <v>3.8668</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2.4889</v>
       </c>
       <c r="D14" t="n">
         <v>1.1407</v>
@@ -1097,7 +1097,7 @@
         <v>3.806</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2.4498</v>
       </c>
       <c r="D15" t="n">
         <v>1.1162</v>
@@ -1143,7 +1143,7 @@
         <v>3.6267</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.3344</v>
       </c>
       <c r="D16" t="n">
         <v>1.0437</v>
@@ -1189,7 +1189,7 @@
         <v>3.3275</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2.1418</v>
       </c>
       <c r="D17" t="n">
         <v>0.9229000000000001</v>
@@ -1235,7 +1235,7 @@
         <v>3.2371</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2.0836</v>
       </c>
       <c r="D18" t="n">
         <v>0.8864</v>
@@ -1281,7 +1281,7 @@
         <v>3.0445</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.9596</v>
       </c>
       <c r="D19" t="n">
         <v>0.8085</v>
@@ -1327,7 +1327,7 @@
         <v>2.8692</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.8468</v>
       </c>
       <c r="D20" t="n">
         <v>0.7377</v>
@@ -1373,7 +1373,7 @@
         <v>2.7639</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.779</v>
       </c>
       <c r="D21" t="n">
         <v>0.6952</v>
@@ -1419,7 +1419,7 @@
         <v>2.6293</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.6924</v>
       </c>
       <c r="D22" t="n">
         <v>0.6408</v>
@@ -1465,7 +1465,7 @@
         <v>2.3963</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.5424</v>
       </c>
       <c r="D23" t="n">
         <v>0.5467</v>
@@ -1511,7 +1511,7 @@
         <v>2.3254</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.4968</v>
       </c>
       <c r="D24" t="n">
         <v>0.518</v>
@@ -1557,7 +1557,7 @@
         <v>2.2565</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.4524</v>
       </c>
       <c r="D25" t="n">
         <v>0.4902</v>
@@ -1603,7 +1603,7 @@
         <v>2.1452</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.3808</v>
       </c>
       <c r="D26" t="n">
         <v>0.4453</v>
@@ -1649,7 +1649,7 @@
         <v>2.057</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.324</v>
       </c>
       <c r="D27" t="n">
         <v>0.4096</v>
@@ -1695,7 +1695,7 @@
         <v>1.9635</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.2638</v>
       </c>
       <c r="D28" t="n">
         <v>0.3718</v>
@@ -1741,7 +1741,7 @@
         <v>1.9262</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1.2398</v>
       </c>
       <c r="D29" t="n">
         <v>0.3568</v>
@@ -1787,7 +1787,7 @@
         <v>1.635</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1.0524</v>
       </c>
       <c r="D30" t="n">
         <v>0.2391</v>
@@ -1833,7 +1833,7 @@
         <v>1.2456</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.8018</v>
       </c>
       <c r="D31" t="n">
         <v>0.0818</v>
@@ -1879,7 +1879,7 @@
         <v>1.1946</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.7689</v>
       </c>
       <c r="D32" t="n">
         <v>0.0612</v>
@@ -1925,7 +1925,7 @@
         <v>1.1013</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.7089</v>
       </c>
       <c r="D33" t="n">
         <v>0.0235</v>
@@ -1971,7 +1971,7 @@
         <v>1.0472</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
       <c r="D34" t="n">
         <v>0.0017</v>
@@ -2017,7 +2017,7 @@
         <v>0.9944</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.6401</v>
       </c>
       <c r="D35" t="n">
         <v>-0.0196</v>
@@ -2063,7 +2063,7 @@
         <v>0.8495</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.5468</v>
       </c>
       <c r="D36" t="n">
         <v>-0.07820000000000001</v>
@@ -2109,7 +2109,7 @@
         <v>0.8447</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.5437</v>
       </c>
       <c r="D37" t="n">
         <v>-0.0801</v>
@@ -2155,7 +2155,7 @@
         <v>0.7771</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.5002</v>
       </c>
       <c r="D38" t="n">
         <v>-0.1074</v>
@@ -2201,7 +2201,7 @@
         <v>0.7302</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="D39" t="n">
         <v>-0.1264</v>
@@ -2247,7 +2247,7 @@
         <v>0.6987</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.4497</v>
       </c>
       <c r="D40" t="n">
         <v>-0.1391</v>
@@ -2293,7 +2293,7 @@
         <v>0.6307</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="D41" t="n">
         <v>-0.1666</v>
@@ -2339,7 +2339,7 @@
         <v>0.3648</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.2348</v>
       </c>
       <c r="D42" t="n">
         <v>-0.274</v>
@@ -2385,7 +2385,7 @@
         <v>0.3233</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.2081</v>
       </c>
       <c r="D43" t="n">
         <v>-0.2908</v>
@@ -2431,7 +2431,7 @@
         <v>0.2984</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.1921</v>
       </c>
       <c r="D44" t="n">
         <v>-0.3008</v>
@@ -2477,7 +2477,7 @@
         <v>0.1785</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.1149</v>
       </c>
       <c r="D45" t="n">
         <v>-0.3493</v>
@@ -2523,7 +2523,7 @@
         <v>0.1645</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.1059</v>
       </c>
       <c r="D46" t="n">
         <v>-0.3549</v>
@@ -2569,7 +2569,7 @@
         <v>0.0184</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.0118</v>
       </c>
       <c r="D47" t="n">
         <v>-0.4139</v>
@@ -2615,7 +2615,7 @@
         <v>-0.0496</v>
       </c>
       <c r="C48" t="n">
-        <v>-0</v>
+        <v>-0.0319</v>
       </c>
       <c r="D48" t="n">
         <v>-0.4414</v>
@@ -2661,7 +2661,7 @@
         <v>-0.0643</v>
       </c>
       <c r="C49" t="n">
-        <v>-0</v>
+        <v>-0.0414</v>
       </c>
       <c r="D49" t="n">
         <v>-0.4473</v>
@@ -2707,7 +2707,7 @@
         <v>-0.2008</v>
       </c>
       <c r="C50" t="n">
-        <v>-0</v>
+        <v>-0.1292</v>
       </c>
       <c r="D50" t="n">
         <v>-0.5024999999999999</v>
@@ -2753,7 +2753,7 @@
         <v>-0.2326</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.1497</v>
       </c>
       <c r="D51" t="n">
         <v>-0.5153</v>
@@ -2799,7 +2799,7 @@
         <v>-0.3819</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.2458</v>
       </c>
       <c r="D52" t="n">
         <v>-0.5756</v>
@@ -2845,7 +2845,7 @@
         <v>-0.3939</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.2535</v>
       </c>
       <c r="D53" t="n">
         <v>-0.5805</v>
@@ -2891,7 +2891,7 @@
         <v>-0.4444</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.286</v>
       </c>
       <c r="D54" t="n">
         <v>-0.6009</v>
@@ -2937,7 +2937,7 @@
         <v>-0.7201</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.4635</v>
       </c>
       <c r="D55" t="n">
         <v>-0.7123</v>
@@ -2983,7 +2983,7 @@
         <v>-0.7529</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.4846</v>
       </c>
       <c r="D56" t="n">
         <v>-0.7255</v>
@@ -3029,7 +3029,7 @@
         <v>-0.843</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.5426</v>
       </c>
       <c r="D57" t="n">
         <v>-0.7619</v>
@@ -3075,7 +3075,7 @@
         <v>-0.9684</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.6233</v>
       </c>
       <c r="D58" t="n">
         <v>-0.8126</v>
@@ -3121,7 +3121,7 @@
         <v>-1.0094</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="D59" t="n">
         <v>-0.8290999999999999</v>
@@ -3167,7 +3167,7 @@
         <v>-1.0289</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.6623</v>
       </c>
       <c r="D60" t="n">
         <v>-0.837</v>
@@ -3213,7 +3213,7 @@
         <v>-1.0427</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.6712</v>
       </c>
       <c r="D61" t="n">
         <v>-0.8426</v>
@@ -3259,7 +3259,7 @@
         <v>-1.0431</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.6714</v>
       </c>
       <c r="D62" t="n">
         <v>-0.8428</v>
@@ -3305,7 +3305,7 @@
         <v>-1.0941</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.7042</v>
       </c>
       <c r="D63" t="n">
         <v>-0.8633999999999999</v>
@@ -3351,7 +3351,7 @@
         <v>-1.205</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.7756</v>
       </c>
       <c r="D64" t="n">
         <v>-0.9082</v>
@@ -3397,7 +3397,7 @@
         <v>-1.3314</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.857</v>
       </c>
       <c r="D65" t="n">
         <v>-0.9592000000000001</v>
@@ -3443,7 +3443,7 @@
         <v>-1.3579</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.874</v>
       </c>
       <c r="D66" t="n">
         <v>-0.9699</v>
@@ -3489,7 +3489,7 @@
         <v>-1.3835</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.8905</v>
       </c>
       <c r="D67" t="n">
         <v>-0.9802999999999999</v>
@@ -3535,7 +3535,7 @@
         <v>-1.4669</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.9442</v>
       </c>
       <c r="D68" t="n">
         <v>-1.014</v>
@@ -3581,7 +3581,7 @@
         <v>-1.4977</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.964</v>
       </c>
       <c r="D69" t="n">
         <v>-1.0264</v>
@@ -3627,7 +3627,7 @@
         <v>-1.5513</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="D70" t="n">
         <v>-1.0481</v>
@@ -3673,7 +3673,7 @@
         <v>-1.7561</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-1.1303</v>
       </c>
       <c r="D71" t="n">
         <v>-1.1308</v>
@@ -3719,7 +3719,7 @@
         <v>-1.8028</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-1.1604</v>
       </c>
       <c r="D72" t="n">
         <v>-1.1497</v>
@@ -3765,7 +3765,7 @@
         <v>-1.8093</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-1.1646</v>
       </c>
       <c r="D73" t="n">
         <v>-1.1523</v>
@@ -3811,7 +3811,7 @@
         <v>-1.8301</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-1.178</v>
       </c>
       <c r="D74" t="n">
         <v>-1.1607</v>
@@ -3857,7 +3857,7 @@
         <v>-1.9247</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.2389</v>
       </c>
       <c r="D75" t="n">
         <v>-1.1989</v>
@@ -3903,7 +3903,7 @@
         <v>-1.9906</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.2813</v>
       </c>
       <c r="D76" t="n">
         <v>-1.2255</v>
@@ -3949,7 +3949,7 @@
         <v>-2.0385</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.3121</v>
       </c>
       <c r="D77" t="n">
         <v>-1.2449</v>
@@ -3995,7 +3995,7 @@
         <v>-2.2791</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.467</v>
       </c>
       <c r="D78" t="n">
         <v>-1.3421</v>
@@ -4041,7 +4041,7 @@
         <v>-3.1755</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-2.044</v>
       </c>
       <c r="D79" t="n">
         <v>-1.7042</v>
@@ -4087,7 +4087,7 @@
         <v>-4.7073</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-3.0299</v>
       </c>
       <c r="D80" t="n">
         <v>-2.323</v>
@@ -4133,7 +4133,7 @@
         <v>-5.1939</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-3.3431</v>
       </c>
       <c r="D81" t="n">
         <v>-2.5196</v>

--- a/database/event/8042/event_8042_evp_summary.xlsx
+++ b/database/event/8042/event_8042_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.718500000000001</v>
+        <v>10.7736</v>
       </c>
       <c r="C2" t="n">
-        <v>6.2555</v>
+        <v>6.9346</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5047</v>
+        <v>3.8483</v>
       </c>
       <c r="E2" t="n">
-        <v>9.718500000000001</v>
+        <v>10.7736</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1812</v>
+        <v>4.2972</v>
       </c>
       <c r="G2" t="n">
-        <v>6.5372</v>
+        <v>6.4764</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1812</v>
+        <v>4.4349</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1812</v>
+        <v>4.4349</v>
       </c>
       <c r="J2" t="n">
-        <v>7.0207</v>
+        <v>6.4764</v>
       </c>
       <c r="K2" t="n">
         <v>100</v>
@@ -529,7 +529,7 @@
         <v>164</v>
       </c>
       <c r="M2" t="n">
-        <v>10.2019</v>
+        <v>10.9113</v>
       </c>
       <c r="N2" t="n">
         <v>264</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.4213</v>
+        <v>10.6185</v>
       </c>
       <c r="C3" t="n">
-        <v>6.0642</v>
+        <v>6.8348</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3846</v>
+        <v>3.7865</v>
       </c>
       <c r="E3" t="n">
-        <v>9.4213</v>
+        <v>10.6185</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9448</v>
+        <v>4.0813</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4764</v>
+        <v>6.5372</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9448</v>
+        <v>4.0964</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9448</v>
+        <v>4.0964</v>
       </c>
       <c r="J3" t="n">
-        <v>6.4764</v>
+        <v>7.0207</v>
       </c>
       <c r="K3" t="n">
         <v>100</v>
@@ -575,7 +575,7 @@
         <v>164</v>
       </c>
       <c r="M3" t="n">
-        <v>9.421199999999999</v>
+        <v>11.1171</v>
       </c>
       <c r="N3" t="n">
         <v>264</v>
@@ -584,139 +584,139 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.3255</v>
+        <v>8.0177</v>
       </c>
       <c r="C4" t="n">
-        <v>4.7152</v>
+        <v>5.1607</v>
       </c>
       <c r="D4" t="n">
-        <v>2.538</v>
+        <v>2.7503</v>
       </c>
       <c r="E4" t="n">
-        <v>7.3255</v>
+        <v>8.0177</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1899</v>
+        <v>4.8371</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1356</v>
+        <v>3.1806</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1899</v>
+        <v>5.2816</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1899</v>
+        <v>5.2816</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1356</v>
+        <v>3.1806</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L4" t="n">
-        <v>164</v>
+        <v>102</v>
       </c>
       <c r="M4" t="n">
-        <v>7.3255</v>
+        <v>8.462199999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>264</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.0202</v>
+        <v>7.4445</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5187</v>
+        <v>4.7918</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4146</v>
+        <v>2.522</v>
       </c>
       <c r="E5" t="n">
-        <v>7.0202</v>
+        <v>7.4445</v>
       </c>
       <c r="F5" t="n">
-        <v>4.416</v>
+        <v>2.3089</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6042</v>
+        <v>5.1356</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6213</v>
+        <v>2.3089</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6213</v>
+        <v>2.3089</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6042</v>
+        <v>5.1356</v>
       </c>
       <c r="K5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="M5" t="n">
-        <v>7.2255</v>
+        <v>7.4445</v>
       </c>
       <c r="N5" t="n">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.6647</v>
+        <v>7.0204</v>
       </c>
       <c r="C6" t="n">
-        <v>4.2898</v>
+        <v>4.5188</v>
       </c>
       <c r="D6" t="n">
-        <v>2.271</v>
+        <v>2.353</v>
       </c>
       <c r="E6" t="n">
-        <v>6.6647</v>
+        <v>7.0204</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4842</v>
+        <v>4.4162</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1806</v>
+        <v>2.6042</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4842</v>
+        <v>4.6216</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4842</v>
+        <v>4.6216</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1806</v>
+        <v>2.6042</v>
       </c>
       <c r="K6" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="L6" t="n">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="M6" t="n">
-        <v>6.6648</v>
+        <v>7.2258</v>
       </c>
       <c r="N6" t="n">
-        <v>206</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.7334</v>
+        <v>6.6292</v>
       </c>
       <c r="C7" t="n">
-        <v>3.6904</v>
+        <v>4.267</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8948</v>
+        <v>2.1972</v>
       </c>
       <c r="E7" t="n">
-        <v>5.7334</v>
+        <v>6.6292</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7495</v>
+        <v>2.6452</v>
       </c>
       <c r="G7" t="n">
         <v>3.984</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7495</v>
+        <v>2.6452</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7576</v>
+        <v>2.6675</v>
       </c>
       <c r="J7" t="n">
         <v>3.984</v>
@@ -759,7 +759,7 @@
         <v>174</v>
       </c>
       <c r="M7" t="n">
-        <v>5.7416</v>
+        <v>6.6515</v>
       </c>
       <c r="N7" t="n">
         <v>317</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.5229</v>
+        <v>6.1527</v>
       </c>
       <c r="C8" t="n">
-        <v>3.5549</v>
+        <v>3.9603</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8098</v>
+        <v>2.0073</v>
       </c>
       <c r="E8" t="n">
-        <v>5.5229</v>
+        <v>6.1527</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7771</v>
+        <v>2.2216</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7458</v>
+        <v>3.9311</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7771</v>
+        <v>2.2216</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7771</v>
+        <v>2.2216</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7458</v>
+        <v>3.9311</v>
       </c>
       <c r="K8" t="n">
         <v>150</v>
@@ -805,7 +805,7 @@
         <v>126</v>
       </c>
       <c r="M8" t="n">
-        <v>5.5229</v>
+        <v>6.152699999999999</v>
       </c>
       <c r="N8" t="n">
         <v>276</v>
@@ -814,277 +814,277 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.3683</v>
+        <v>5.9864</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4554</v>
+        <v>3.8532</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7473</v>
+        <v>1.9411</v>
       </c>
       <c r="E9" t="n">
-        <v>5.3683</v>
+        <v>5.9864</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6921</v>
+        <v>4.2406</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6762</v>
+        <v>1.7458</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6921</v>
+        <v>4.3462</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>4.3462</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6762</v>
+        <v>1.7458</v>
       </c>
       <c r="K9" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="L9" t="n">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3762</v>
+        <v>6.092</v>
       </c>
       <c r="N9" t="n">
-        <v>317</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.1873</v>
+        <v>5.362</v>
       </c>
       <c r="C10" t="n">
-        <v>3.3389</v>
+        <v>3.4513</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6742</v>
+        <v>1.6923</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1873</v>
+        <v>5.362</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2562</v>
+        <v>1.6858</v>
       </c>
       <c r="G10" t="n">
-        <v>3.9311</v>
+        <v>3.6762</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2562</v>
+        <v>1.6858</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2562</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9311</v>
+        <v>3.6762</v>
       </c>
       <c r="K10" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="L10" t="n">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="M10" t="n">
-        <v>5.1873</v>
+        <v>5.3762</v>
       </c>
       <c r="N10" t="n">
-        <v>276</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.739</v>
+        <v>4.8809</v>
       </c>
       <c r="C11" t="n">
-        <v>3.0503</v>
+        <v>3.1417</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4931</v>
+        <v>1.5006</v>
       </c>
       <c r="E11" t="n">
-        <v>4.739</v>
+        <v>4.8809</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4158</v>
+        <v>4.4935</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3232</v>
+        <v>0.3874</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4158</v>
+        <v>4.7428</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4271</v>
+        <v>4.7827</v>
       </c>
       <c r="J11" t="n">
-        <v>2.3232</v>
+        <v>0.3874</v>
       </c>
       <c r="K11" t="n">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="L11" t="n">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="M11" t="n">
-        <v>4.750299999999999</v>
+        <v>5.170100000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>317</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.2215</v>
+        <v>4.8443</v>
       </c>
       <c r="C12" t="n">
-        <v>2.7172</v>
+        <v>3.1181</v>
       </c>
       <c r="D12" t="n">
-        <v>1.284</v>
+        <v>1.4861</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2215</v>
+        <v>4.8443</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8341</v>
+        <v>2.5211</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3874</v>
+        <v>2.3232</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8341</v>
+        <v>2.5211</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8519</v>
+        <v>2.5423</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3874</v>
+        <v>2.3232</v>
       </c>
       <c r="K12" t="n">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="L12" t="n">
-        <v>45</v>
+        <v>174</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2393</v>
+        <v>4.8655</v>
       </c>
       <c r="N12" t="n">
-        <v>228</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kvem</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.0797</v>
+        <v>4.2708</v>
       </c>
       <c r="C13" t="n">
-        <v>2.626</v>
+        <v>2.749</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2267</v>
+        <v>1.2576</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0797</v>
+        <v>4.2708</v>
       </c>
       <c r="F13" t="n">
-        <v>4.0797</v>
+        <v>3.5959</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>4.0939</v>
+        <v>3.5959</v>
       </c>
       <c r="I13" t="n">
-        <v>4.0939</v>
+        <v>3.5959</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M13" t="n">
-        <v>4.0939</v>
+        <v>4.270799999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>178</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.8668</v>
+        <v>4.2246</v>
       </c>
       <c r="C14" t="n">
-        <v>2.4889</v>
+        <v>2.7192</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1407</v>
+        <v>1.2392</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8668</v>
+        <v>4.2246</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1919</v>
+        <v>3.8447</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.3799</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1919</v>
+        <v>3.8447</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1919</v>
+        <v>3.8447</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.3799</v>
       </c>
       <c r="K14" t="n">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="L14" t="n">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8668</v>
+        <v>4.2246</v>
       </c>
       <c r="N14" t="n">
-        <v>206</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.806</v>
+        <v>4.0877</v>
       </c>
       <c r="C15" t="n">
-        <v>2.4498</v>
+        <v>2.6311</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1162</v>
+        <v>1.1846</v>
       </c>
       <c r="E15" t="n">
-        <v>3.806</v>
+        <v>4.0877</v>
       </c>
       <c r="F15" t="n">
-        <v>3.806</v>
+        <v>4.0877</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.806</v>
+        <v>4.1064</v>
       </c>
       <c r="I15" t="n">
-        <v>3.806</v>
+        <v>4.1064</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.806</v>
+        <v>4.1064</v>
       </c>
       <c r="N15" t="n">
         <v>147</v>
@@ -1136,645 +1136,645 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>Kvem</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.6267</v>
+        <v>4.0797</v>
       </c>
       <c r="C16" t="n">
-        <v>2.3344</v>
+        <v>2.626</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0437</v>
+        <v>1.1814</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6267</v>
+        <v>4.0797</v>
       </c>
       <c r="F16" t="n">
-        <v>3.9408</v>
+        <v>4.0797</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3141</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9408</v>
+        <v>4.0939</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9591</v>
+        <v>4.0939</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3141</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="L16" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.645</v>
+        <v>4.0939</v>
       </c>
       <c r="N16" t="n">
-        <v>317</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.3275</v>
+        <v>3.9647</v>
       </c>
       <c r="C17" t="n">
-        <v>2.1418</v>
+        <v>2.5519</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9229000000000001</v>
+        <v>1.1356</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3275</v>
+        <v>3.9647</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9476</v>
+        <v>4.2788</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3799</v>
+        <v>-0.3141</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9476</v>
+        <v>4.406</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9476</v>
+        <v>4.4431</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3799</v>
+        <v>-0.3141</v>
       </c>
       <c r="K17" t="n">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="L17" t="n">
-        <v>63</v>
+        <v>174</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3275</v>
+        <v>4.129</v>
       </c>
       <c r="N17" t="n">
-        <v>138</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.2371</v>
+        <v>3.8943</v>
       </c>
       <c r="C18" t="n">
-        <v>2.0836</v>
+        <v>2.5066</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8864</v>
+        <v>1.1076</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2371</v>
+        <v>3.8943</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2121</v>
+        <v>4.1743</v>
       </c>
       <c r="G18" t="n">
-        <v>1.025</v>
+        <v>-0.28</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2121</v>
+        <v>4.2423</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2121</v>
+        <v>4.278</v>
       </c>
       <c r="J18" t="n">
-        <v>1.025</v>
+        <v>-0.28</v>
       </c>
       <c r="K18" t="n">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="L18" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2371</v>
+        <v>3.997999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>143</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.0445</v>
+        <v>3.6763</v>
       </c>
       <c r="C19" t="n">
-        <v>1.9596</v>
+        <v>2.3663</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8085</v>
+        <v>1.0207</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0445</v>
+        <v>3.6763</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0445</v>
+        <v>3.8533</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.177</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0445</v>
+        <v>3.8533</v>
       </c>
       <c r="I19" t="n">
-        <v>3.0445</v>
+        <v>3.8857</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.177</v>
       </c>
       <c r="K19" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M19" t="n">
-        <v>3.0445</v>
+        <v>3.7087</v>
       </c>
       <c r="N19" t="n">
-        <v>178</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.8692</v>
+        <v>3.4262</v>
       </c>
       <c r="C20" t="n">
-        <v>1.8468</v>
+        <v>2.2053</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7377</v>
+        <v>0.9211</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8692</v>
+        <v>3.4262</v>
       </c>
       <c r="F20" t="n">
-        <v>3.233</v>
+        <v>4.3033</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3638</v>
+        <v>-0.8771</v>
       </c>
       <c r="H20" t="n">
-        <v>3.233</v>
+        <v>4.4445</v>
       </c>
       <c r="I20" t="n">
-        <v>3.248</v>
+        <v>4.4445</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3638</v>
+        <v>-0.8771</v>
       </c>
       <c r="K20" t="n">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="L20" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8842</v>
+        <v>3.5674</v>
       </c>
       <c r="N20" t="n">
-        <v>219</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.7639</v>
+        <v>3.331</v>
       </c>
       <c r="C21" t="n">
-        <v>1.779</v>
+        <v>2.1441</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6952</v>
+        <v>0.8832</v>
       </c>
       <c r="E21" t="n">
-        <v>2.7639</v>
+        <v>3.331</v>
       </c>
       <c r="F21" t="n">
-        <v>2.9409</v>
+        <v>3.6948</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.177</v>
+        <v>-0.3638</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9409</v>
+        <v>3.6948</v>
       </c>
       <c r="I21" t="n">
-        <v>2.9545</v>
+        <v>3.7259</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.177</v>
+        <v>-0.3638</v>
       </c>
       <c r="K21" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="L21" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M21" t="n">
-        <v>2.7775</v>
+        <v>3.3621</v>
       </c>
       <c r="N21" t="n">
-        <v>228</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.6293</v>
+        <v>3.3143</v>
       </c>
       <c r="C22" t="n">
-        <v>1.6924</v>
+        <v>2.1333</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6408</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6293</v>
+        <v>3.3143</v>
       </c>
       <c r="F22" t="n">
-        <v>2.9093</v>
+        <v>1.1077</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.28</v>
+        <v>2.2066</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9093</v>
+        <v>1.1077</v>
       </c>
       <c r="I22" t="n">
-        <v>2.9228</v>
+        <v>1.1077</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.28</v>
+        <v>2.2066</v>
       </c>
       <c r="K22" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>39</v>
+        <v>164</v>
       </c>
       <c r="M22" t="n">
-        <v>2.6428</v>
+        <v>3.3143</v>
       </c>
       <c r="N22" t="n">
-        <v>219</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.3963</v>
+        <v>3.2371</v>
       </c>
       <c r="C23" t="n">
-        <v>1.5424</v>
+        <v>2.0836</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5467</v>
+        <v>0.8458</v>
       </c>
       <c r="E23" t="n">
-        <v>2.3963</v>
+        <v>3.2371</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1018</v>
+        <v>2.2121</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2945</v>
+        <v>1.025</v>
       </c>
       <c r="H23" t="n">
-        <v>2.1018</v>
+        <v>2.2121</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1116</v>
+        <v>2.2121</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2945</v>
+        <v>1.025</v>
       </c>
       <c r="K23" t="n">
-        <v>183</v>
+        <v>108</v>
       </c>
       <c r="L23" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="M23" t="n">
-        <v>2.4061</v>
+        <v>3.2371</v>
       </c>
       <c r="N23" t="n">
-        <v>228</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.3254</v>
+        <v>3.0655</v>
       </c>
       <c r="C24" t="n">
-        <v>1.4968</v>
+        <v>1.9732</v>
       </c>
       <c r="D24" t="n">
-        <v>0.518</v>
+        <v>0.7774</v>
       </c>
       <c r="E24" t="n">
-        <v>2.3254</v>
+        <v>3.0655</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9394</v>
+        <v>2.771</v>
       </c>
       <c r="G24" t="n">
-        <v>0.386</v>
+        <v>0.2945</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9394</v>
+        <v>2.771</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9484</v>
+        <v>2.7944</v>
       </c>
       <c r="J24" t="n">
-        <v>0.386</v>
+        <v>0.2945</v>
       </c>
       <c r="K24" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="L24" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="M24" t="n">
-        <v>2.3344</v>
+        <v>3.0889</v>
       </c>
       <c r="N24" t="n">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>controlez</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.2565</v>
+        <v>3.0445</v>
       </c>
       <c r="C25" t="n">
-        <v>1.4524</v>
+        <v>1.9596</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4902</v>
+        <v>0.769</v>
       </c>
       <c r="E25" t="n">
-        <v>2.2565</v>
+        <v>3.0445</v>
       </c>
       <c r="F25" t="n">
-        <v>3.2565</v>
+        <v>3.0445</v>
       </c>
       <c r="G25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2565</v>
+        <v>3.0445</v>
       </c>
       <c r="I25" t="n">
-        <v>3.2565</v>
+        <v>3.0445</v>
       </c>
       <c r="J25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="L25" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.2565</v>
+        <v>3.0445</v>
       </c>
       <c r="N25" t="n">
-        <v>143</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>try</t>
+          <t>controlez</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.1452</v>
+        <v>2.541</v>
       </c>
       <c r="C26" t="n">
-        <v>1.3808</v>
+        <v>1.6356</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4453</v>
+        <v>0.5684</v>
       </c>
       <c r="E26" t="n">
-        <v>2.1452</v>
+        <v>2.541</v>
       </c>
       <c r="F26" t="n">
-        <v>2.1452</v>
+        <v>3.541</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H26" t="n">
-        <v>2.1452</v>
+        <v>3.541</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1452</v>
+        <v>3.541</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K26" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M26" t="n">
-        <v>2.1452</v>
+        <v>2.541</v>
       </c>
       <c r="N26" t="n">
-        <v>106</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.057</v>
+        <v>2.3951</v>
       </c>
       <c r="C27" t="n">
-        <v>1.324</v>
+        <v>1.5416</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4096</v>
+        <v>0.5103</v>
       </c>
       <c r="E27" t="n">
-        <v>2.057</v>
+        <v>2.3951</v>
       </c>
       <c r="F27" t="n">
-        <v>2.9341</v>
+        <v>2.3951</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.8771</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.9341</v>
+        <v>2.3951</v>
       </c>
       <c r="I27" t="n">
-        <v>2.9341</v>
+        <v>2.3951</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.8771</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="L27" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.057</v>
+        <v>2.3951</v>
       </c>
       <c r="N27" t="n">
-        <v>138</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.9635</v>
+        <v>2.3182</v>
       </c>
       <c r="C28" t="n">
-        <v>1.2638</v>
+        <v>1.4921</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3718</v>
+        <v>0.4797</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9635</v>
+        <v>2.3182</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2431</v>
+        <v>1.9322</v>
       </c>
       <c r="G28" t="n">
-        <v>2.2066</v>
+        <v>0.386</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2431</v>
+        <v>1.9322</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2431</v>
+        <v>1.9484</v>
       </c>
       <c r="J28" t="n">
-        <v>2.2066</v>
+        <v>0.386</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="L28" t="n">
-        <v>164</v>
+        <v>39</v>
       </c>
       <c r="M28" t="n">
-        <v>1.9635</v>
+        <v>2.3344</v>
       </c>
       <c r="N28" t="n">
-        <v>264</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>try</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9262</v>
+        <v>2.1452</v>
       </c>
       <c r="C29" t="n">
-        <v>1.2398</v>
+        <v>1.3808</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3568</v>
+        <v>0.4107</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9262</v>
+        <v>2.1452</v>
       </c>
       <c r="F29" t="n">
-        <v>1.9262</v>
+        <v>2.1452</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.9262</v>
+        <v>2.1452</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9262</v>
+        <v>2.1452</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.9262</v>
+        <v>2.1452</v>
       </c>
       <c r="N29" t="n">
-        <v>181</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30">
@@ -1790,7 +1790,7 @@
         <v>1.0524</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2391</v>
+        <v>0.2075</v>
       </c>
       <c r="E30" t="n">
         <v>1.635</v>
@@ -1826,875 +1826,875 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2456</v>
+        <v>1.5552</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8018</v>
+        <v>1.001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0818</v>
+        <v>0.1757</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2456</v>
+        <v>1.5552</v>
       </c>
       <c r="F31" t="n">
-        <v>1.8928</v>
+        <v>1.5552</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.6472</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.8928</v>
+        <v>1.5552</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8928</v>
+        <v>1.5552</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.6472</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="L31" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.2456</v>
+        <v>1.5552</v>
       </c>
       <c r="N31" t="n">
-        <v>138</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1946</v>
+        <v>1.5473</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7689</v>
+        <v>0.9959</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0612</v>
+        <v>0.1725</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1946</v>
+        <v>1.5473</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1656</v>
+        <v>1.5473</v>
       </c>
       <c r="G32" t="n">
-        <v>1.3602</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1656</v>
+        <v>1.5473</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1656</v>
+        <v>1.5473</v>
       </c>
       <c r="J32" t="n">
-        <v>1.3602</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="L32" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1946</v>
+        <v>1.5473</v>
       </c>
       <c r="N32" t="n">
-        <v>276</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1013</v>
+        <v>1.5233</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7089</v>
+        <v>0.9805</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0235</v>
+        <v>0.163</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1013</v>
+        <v>1.5233</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1013</v>
+        <v>0.1631</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1.3602</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1013</v>
+        <v>0.1631</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1013</v>
+        <v>0.1631</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1.3602</v>
       </c>
       <c r="K33" t="n">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1013</v>
+        <v>1.5233</v>
       </c>
       <c r="N33" t="n">
-        <v>181</v>
+        <v>276</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0472</v>
+        <v>1.4726</v>
       </c>
       <c r="C34" t="n">
-        <v>0.674</v>
+        <v>0.9479</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0017</v>
+        <v>0.1428</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0472</v>
+        <v>1.4726</v>
       </c>
       <c r="F34" t="n">
-        <v>1.9854</v>
+        <v>2.1198</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.9382</v>
+        <v>-0.6472</v>
       </c>
       <c r="H34" t="n">
-        <v>1.9854</v>
+        <v>2.1198</v>
       </c>
       <c r="I34" t="n">
-        <v>1.9946</v>
+        <v>2.1198</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9382</v>
+        <v>-0.6472</v>
       </c>
       <c r="K34" t="n">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="L34" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0564</v>
+        <v>1.4726</v>
       </c>
       <c r="N34" t="n">
-        <v>219</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9944</v>
+        <v>1.4079</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6401</v>
+        <v>0.9062</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0196</v>
+        <v>0.117</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9944</v>
+        <v>1.4079</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9944</v>
+        <v>2.1296</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.7217</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9944</v>
+        <v>2.1296</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9944</v>
+        <v>2.1296</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.7217</v>
       </c>
       <c r="K35" t="n">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9944</v>
+        <v>1.4079</v>
       </c>
       <c r="N35" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8495</v>
+        <v>1.1719</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5468</v>
+        <v>0.7543</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.023</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8495</v>
+        <v>1.1719</v>
       </c>
       <c r="F36" t="n">
-        <v>1.5712</v>
+        <v>1.1719</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.7217</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.5712</v>
+        <v>1.1719</v>
       </c>
       <c r="I36" t="n">
-        <v>1.5712</v>
+        <v>1.1719</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.7217</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="L36" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8494999999999999</v>
+        <v>1.1719</v>
       </c>
       <c r="N36" t="n">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>xiELO</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8447</v>
+        <v>1.0398</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5437</v>
+        <v>0.6693</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0801</v>
+        <v>-0.0297</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8447</v>
+        <v>1.0398</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8447</v>
+        <v>1.978</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.9382</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8447</v>
+        <v>1.978</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8447</v>
+        <v>1.9946</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.9382</v>
       </c>
       <c r="K37" t="n">
-        <v>119</v>
+        <v>180</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8447</v>
+        <v>1.0564</v>
       </c>
       <c r="N37" t="n">
-        <v>119</v>
+        <v>219</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7771</v>
+        <v>0.9324</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5002</v>
+        <v>0.6002</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1074</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7771</v>
+        <v>0.9324</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7771</v>
+        <v>0.9324</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7771</v>
+        <v>0.9324</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7771</v>
+        <v>0.9324</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7771</v>
+        <v>0.9324</v>
       </c>
       <c r="N38" t="n">
-        <v>127</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7302</v>
+        <v>0.8659</v>
       </c>
       <c r="C39" t="n">
-        <v>0.47</v>
+        <v>0.5574</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1264</v>
+        <v>-0.0989</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7302</v>
+        <v>0.8659</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7302</v>
+        <v>0.9892</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.1233</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7302</v>
+        <v>0.9892</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7302</v>
+        <v>0.9892</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.1233</v>
       </c>
       <c r="K39" t="n">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7302</v>
+        <v>0.8659</v>
       </c>
       <c r="N39" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>alex666</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6987</v>
+        <v>0.8455</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4497</v>
+        <v>0.5442</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1391</v>
+        <v>-0.1071</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6987</v>
+        <v>0.8455</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.7814</v>
+        <v>0.8455</v>
       </c>
       <c r="G40" t="n">
-        <v>1.4801</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.7814</v>
+        <v>0.8455</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7814</v>
+        <v>0.8455</v>
       </c>
       <c r="J40" t="n">
-        <v>1.4801</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="L40" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6987</v>
+        <v>0.8455</v>
       </c>
       <c r="N40" t="n">
-        <v>206</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>esenthial</t>
+          <t>xiELO</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6307</v>
+        <v>0.8447</v>
       </c>
       <c r="C41" t="n">
-        <v>0.406</v>
+        <v>0.5437</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1666</v>
+        <v>-0.1074</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6307</v>
+        <v>0.8447</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6307</v>
+        <v>0.8447</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6307</v>
+        <v>0.8447</v>
       </c>
       <c r="I41" t="n">
-        <v>0.6307</v>
+        <v>0.8447</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6307</v>
+        <v>0.8447</v>
       </c>
       <c r="N41" t="n">
-        <v>167</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>alex666</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3648</v>
+        <v>0.7302</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2348</v>
+        <v>0.47</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.274</v>
+        <v>-0.153</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3648</v>
+        <v>0.7302</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3648</v>
+        <v>0.7302</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3648</v>
+        <v>0.7302</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3648</v>
+        <v>0.7302</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3648</v>
+        <v>0.7302</v>
       </c>
       <c r="N42" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kensizor</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3233</v>
+        <v>0.6987</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2081</v>
+        <v>0.4497</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2908</v>
+        <v>-0.1655</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3233</v>
+        <v>0.6987</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3233</v>
+        <v>-0.7814</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1.4801</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3233</v>
+        <v>-0.7814</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3233</v>
+        <v>-0.7814</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1.4801</v>
       </c>
       <c r="K43" t="n">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3233</v>
+        <v>0.6987</v>
       </c>
       <c r="N43" t="n">
-        <v>167</v>
+        <v>206</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>esenthial</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2984</v>
+        <v>0.6307</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1921</v>
+        <v>0.406</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3008</v>
+        <v>-0.1926</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2984</v>
+        <v>0.6307</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2984</v>
+        <v>0.6307</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2984</v>
+        <v>0.6307</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2984</v>
+        <v>0.6307</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2984</v>
+        <v>0.6307</v>
       </c>
       <c r="N44" t="n">
-        <v>181</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>kensizor</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.1785</v>
+        <v>0.3233</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1149</v>
+        <v>0.2081</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3493</v>
+        <v>-0.3151</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1785</v>
+        <v>0.3233</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1785</v>
+        <v>0.3233</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1785</v>
+        <v>0.3233</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1785</v>
+        <v>0.3233</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>90</v>
+        <v>167</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1785</v>
+        <v>0.3233</v>
       </c>
       <c r="N45" t="n">
-        <v>90</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1645</v>
+        <v>0.1785</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1059</v>
+        <v>0.1149</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3549</v>
+        <v>-0.3728</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1645</v>
+        <v>0.1785</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.9253</v>
+        <v>0.1785</v>
       </c>
       <c r="G46" t="n">
-        <v>2.0898</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.9253</v>
+        <v>0.1785</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.9253</v>
+        <v>0.1785</v>
       </c>
       <c r="J46" t="n">
-        <v>2.0898</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="L46" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1644999999999999</v>
+        <v>0.1785</v>
       </c>
       <c r="N46" t="n">
-        <v>206</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0184</v>
+        <v>0.1645</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0118</v>
+        <v>0.1059</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4139</v>
+        <v>-0.3784</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0184</v>
+        <v>0.1645</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0184</v>
+        <v>-1.9253</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>2.0898</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0184</v>
+        <v>-1.9253</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0184</v>
+        <v>-1.9253</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>2.0898</v>
       </c>
       <c r="K47" t="n">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0184</v>
+        <v>0.1644999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>147</v>
+        <v>206</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0496</v>
+        <v>0.0184</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0319</v>
+        <v>0.0118</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4414</v>
+        <v>-0.4366</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0496</v>
+        <v>0.0184</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0496</v>
+        <v>0.0184</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0496</v>
+        <v>0.0184</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0496</v>
+        <v>0.0184</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0496</v>
+        <v>0.0184</v>
       </c>
       <c r="N48" t="n">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0643</v>
+        <v>-0.0496</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0414</v>
+        <v>-0.0319</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4473</v>
+        <v>-0.4637</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0643</v>
+        <v>-0.0496</v>
       </c>
       <c r="F49" t="n">
-        <v>0.059</v>
+        <v>-0.0496</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.1233</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.059</v>
+        <v>-0.0496</v>
       </c>
       <c r="I49" t="n">
-        <v>0.059</v>
+        <v>-0.0496</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.1233</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="L49" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.06430000000000001</v>
+        <v>-0.0496</v>
       </c>
       <c r="N49" t="n">
-        <v>143</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50">
@@ -2710,7 +2710,7 @@
         <v>-0.1292</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.5239</v>
       </c>
       <c r="E50" t="n">
         <v>-0.2008</v>
@@ -2746,78 +2746,78 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.2326</v>
+        <v>-0.2218</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1497</v>
+        <v>-0.1428</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5153</v>
+        <v>-0.5323</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.2326</v>
+        <v>-0.2218</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2326</v>
+        <v>0.738</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.9598</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.2326</v>
+        <v>0.738</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2326</v>
+        <v>0.7442</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-0.9598</v>
       </c>
       <c r="K51" t="n">
-        <v>119</v>
+        <v>183</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.2326</v>
+        <v>-0.2156</v>
       </c>
       <c r="N51" t="n">
-        <v>119</v>
+        <v>228</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.3819</v>
+        <v>-0.2326</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.2458</v>
+        <v>-0.1497</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5756</v>
+        <v>-0.5366</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.3819</v>
+        <v>-0.2326</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.3819</v>
+        <v>-0.2326</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.3819</v>
+        <v>-0.2326</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.3819</v>
+        <v>-0.2326</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.3819</v>
+        <v>-0.2326</v>
       </c>
       <c r="N52" t="n">
         <v>119</v>
@@ -2838,1044 +2838,1044 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3939</v>
+        <v>-0.3819</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2535</v>
+        <v>-0.2458</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5805</v>
+        <v>-0.5961</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3939</v>
+        <v>-0.3819</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3939</v>
+        <v>-0.3819</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3939</v>
+        <v>-0.3819</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3939</v>
+        <v>-0.3819</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3939</v>
+        <v>-0.3819</v>
       </c>
       <c r="N53" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.4444</v>
+        <v>-0.3939</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.286</v>
+        <v>-0.2535</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6009</v>
+        <v>-0.6008</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.4444</v>
+        <v>-0.3939</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5154</v>
+        <v>-0.3939</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.9598</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.5154</v>
+        <v>-0.3939</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5178</v>
+        <v>-0.3939</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.9598</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>183</v>
+        <v>127</v>
       </c>
       <c r="L54" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.4419999999999999</v>
+        <v>-0.3939</v>
       </c>
       <c r="N54" t="n">
-        <v>228</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.7201</v>
+        <v>-0.616</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.4635</v>
+        <v>-0.3965</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.7123</v>
+        <v>-0.6893</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.7201</v>
+        <v>-0.616</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.7201</v>
+        <v>1.384</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.7201</v>
+        <v>1.384</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.7201</v>
+        <v>1.384</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="K55" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.7201</v>
+        <v>-0.6160000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>90</v>
+        <v>206</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.7529</v>
+        <v>-0.7201</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.4846</v>
+        <v>-0.4635</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7255</v>
+        <v>-0.7308</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.7529</v>
+        <v>-0.7201</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1005</v>
+        <v>-0.7201</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.8534</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1005</v>
+        <v>-0.7201</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1005</v>
+        <v>-0.7201</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.8534</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="L56" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.7529</v>
+        <v>-0.7201</v>
       </c>
       <c r="N56" t="n">
-        <v>138</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.843</v>
+        <v>-0.7529</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.5426</v>
+        <v>-0.4846</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7619</v>
+        <v>-0.7439</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.843</v>
+        <v>-0.7529</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.843</v>
+        <v>0.1005</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-0.8534</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.843</v>
+        <v>0.1005</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.843</v>
+        <v>0.1005</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>-0.8534</v>
       </c>
       <c r="K57" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.843</v>
+        <v>-0.7529</v>
       </c>
       <c r="N57" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BELCHONOKK</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.9684</v>
+        <v>-0.843</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.6233</v>
+        <v>-0.5426</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.8126</v>
+        <v>-0.7798</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.9684</v>
+        <v>-0.843</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.9684</v>
+        <v>-0.843</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.9684</v>
+        <v>-0.843</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.9684</v>
+        <v>-0.843</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.9684</v>
+        <v>-0.843</v>
       </c>
       <c r="N58" t="n">
-        <v>119</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.0094</v>
+        <v>-0.9074</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.6497000000000001</v>
+        <v>-0.5841</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.8054</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.0094</v>
+        <v>-0.9074</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.0094</v>
+        <v>-0.9074</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.0094</v>
+        <v>-0.9074</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.0094</v>
+        <v>-0.9074</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.0094</v>
+        <v>-0.9074</v>
       </c>
       <c r="N59" t="n">
-        <v>127</v>
+        <v>106</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>BELCHONOKK</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.0289</v>
+        <v>-0.9684</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.6623</v>
+        <v>-0.6233</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.837</v>
+        <v>-0.8297</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.0289</v>
+        <v>-0.9684</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.0289</v>
+        <v>-0.9684</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.0289</v>
+        <v>-0.9684</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.0289</v>
+        <v>-0.9684</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.0289</v>
+        <v>-0.9684</v>
       </c>
       <c r="N60" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.0427</v>
+        <v>-1.0094</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.6712</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.8426</v>
+        <v>-0.8461</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.0427</v>
+        <v>-1.0094</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.0427</v>
+        <v>-1.0094</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.0427</v>
+        <v>-1.0094</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0427</v>
+        <v>-1.0094</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-1.0427</v>
+        <v>-1.0094</v>
       </c>
       <c r="N61" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-1.0431</v>
+        <v>-1.0289</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.6714</v>
+        <v>-0.6623</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8428</v>
+        <v>-0.8538</v>
       </c>
       <c r="E62" t="n">
-        <v>-1.0431</v>
+        <v>-1.0289</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.0431</v>
+        <v>-1.0289</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-1.0431</v>
+        <v>-1.0289</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0431</v>
+        <v>-1.0289</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-1.0431</v>
+        <v>-1.0289</v>
       </c>
       <c r="N62" t="n">
-        <v>147</v>
+        <v>106</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-1.0941</v>
+        <v>-1.0431</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.7042</v>
+        <v>-0.6714</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.8595</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.0941</v>
+        <v>-1.0431</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.0941</v>
+        <v>-1.0431</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-1.0941</v>
+        <v>-1.0431</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0941</v>
+        <v>-1.0431</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-1.0941</v>
+        <v>-1.0431</v>
       </c>
       <c r="N63" t="n">
-        <v>90</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.205</v>
+        <v>-1.0941</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.7756</v>
+        <v>-0.7042</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.9082</v>
+        <v>-0.8798</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.205</v>
+        <v>-1.0941</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-1.0941</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.5513</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-1.0941</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-1.0941</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.5513</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="L64" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-1.205</v>
+        <v>-1.0941</v>
       </c>
       <c r="N64" t="n">
-        <v>143</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>noway</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.3314</v>
+        <v>-1.1202</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.857</v>
+        <v>-0.721</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9592000000000001</v>
+        <v>-0.8902</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.3314</v>
+        <v>-1.1202</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.3314</v>
+        <v>-1.1202</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.3314</v>
+        <v>-1.1202</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.3314</v>
+        <v>-1.1202</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-1.3314</v>
+        <v>-1.1202</v>
       </c>
       <c r="N65" t="n">
-        <v>106</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.3579</v>
+        <v>-1.205</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.874</v>
+        <v>-0.7756</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9699</v>
+        <v>-0.924</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.3579</v>
+        <v>-1.205</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6421</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="G66" t="n">
-        <v>-2</v>
+        <v>-0.5513</v>
       </c>
       <c r="H66" t="n">
-        <v>0.6421</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>0.6421</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="J66" t="n">
-        <v>-2</v>
+        <v>-0.5513</v>
       </c>
       <c r="K66" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="L66" t="n">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="M66" t="n">
-        <v>-1.3579</v>
+        <v>-1.205</v>
       </c>
       <c r="N66" t="n">
-        <v>206</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AW</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.3835</v>
+        <v>-1.2341</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.8905</v>
+        <v>-0.7943</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9802999999999999</v>
+        <v>-0.9356</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.3835</v>
+        <v>-1.2341</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.3835</v>
+        <v>-1.2341</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.3835</v>
+        <v>-1.2341</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.3835</v>
+        <v>-1.2341</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-1.3835</v>
+        <v>-1.2341</v>
       </c>
       <c r="N67" t="n">
-        <v>119</v>
+        <v>181</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>noway</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.4669</v>
+        <v>-1.3314</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.9442</v>
+        <v>-0.857</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.014</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.4669</v>
+        <v>-1.3314</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.4669</v>
+        <v>-1.3314</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.4669</v>
+        <v>-1.3314</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.4669</v>
+        <v>-1.3314</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.4669</v>
+        <v>-1.3314</v>
       </c>
       <c r="N68" t="n">
-        <v>181</v>
+        <v>106</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>nicx</t>
+          <t>AW</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.4977</v>
+        <v>-1.3835</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.964</v>
+        <v>-0.8905</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0264</v>
+        <v>-0.9951</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.4977</v>
+        <v>-1.3835</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.4977</v>
+        <v>-1.3835</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.4977</v>
+        <v>-1.3835</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.4977</v>
+        <v>-1.3835</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.4977</v>
+        <v>-1.3835</v>
       </c>
       <c r="N69" t="n">
-        <v>178</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>nicx</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.5513</v>
+        <v>-1.4977</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-0.964</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0481</v>
+        <v>-1.0406</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.5513</v>
+        <v>-1.4977</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.5513</v>
+        <v>-1.4977</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.5513</v>
+        <v>-1.4977</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.5513</v>
+        <v>-1.4977</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.5513</v>
+        <v>-1.4977</v>
       </c>
       <c r="N70" t="n">
-        <v>106</v>
+        <v>178</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.7561</v>
+        <v>-1.5513</v>
       </c>
       <c r="C71" t="n">
-        <v>-1.1303</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.1308</v>
+        <v>-1.0619</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.7561</v>
+        <v>-1.5513</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.8466</v>
+        <v>-1.5513</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0905</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.8466</v>
+        <v>-1.5513</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.8466</v>
+        <v>-1.5513</v>
       </c>
       <c r="J71" t="n">
-        <v>0.0905</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="L71" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.7561</v>
+        <v>-1.5513</v>
       </c>
       <c r="N71" t="n">
-        <v>276</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.8028</v>
+        <v>-1.7561</v>
       </c>
       <c r="C72" t="n">
-        <v>-1.1604</v>
+        <v>-1.1303</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1497</v>
+        <v>-1.1435</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.8028</v>
+        <v>-1.7561</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.8028</v>
+        <v>-1.8466</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>0.0905</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.8028</v>
+        <v>-1.8466</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.8028</v>
+        <v>-1.8466</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>0.0905</v>
       </c>
       <c r="K72" t="n">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.8028</v>
+        <v>-1.7561</v>
       </c>
       <c r="N72" t="n">
-        <v>178</v>
+        <v>276</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.8093</v>
+        <v>-1.8028</v>
       </c>
       <c r="C73" t="n">
-        <v>-1.1646</v>
+        <v>-1.1604</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1523</v>
+        <v>-1.1621</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.8093</v>
+        <v>-1.8028</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.8093</v>
+        <v>-1.8028</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.8093</v>
+        <v>-1.8028</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.8093</v>
+        <v>-1.8028</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.8093</v>
+        <v>-1.8028</v>
       </c>
       <c r="N73" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>headtr1ck</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.8301</v>
+        <v>-1.8087</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.178</v>
+        <v>-1.1642</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1607</v>
+        <v>-1.1645</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.8301</v>
+        <v>-1.8087</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.8301</v>
+        <v>-1.8087</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.8301</v>
+        <v>-1.8087</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.8301</v>
+        <v>-1.8087</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.8301</v>
+        <v>-1.8087</v>
       </c>
       <c r="N74" t="n">
-        <v>167</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>headtr1ck</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.9247</v>
+        <v>-1.8301</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.2389</v>
+        <v>-1.178</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1989</v>
+        <v>-1.173</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.9247</v>
+        <v>-1.8301</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.9247</v>
+        <v>-1.8301</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.9247</v>
+        <v>-1.8301</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.9247</v>
+        <v>-1.8301</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.9247</v>
+        <v>-1.8301</v>
       </c>
       <c r="N75" t="n">
         <v>167</v>
@@ -3906,7 +3906,7 @@
         <v>-1.2813</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2255</v>
+        <v>-1.237</v>
       </c>
       <c r="E76" t="n">
         <v>-1.9906</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-2.0385</v>
+        <v>-2.0311</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.3121</v>
+        <v>-1.3073</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2449</v>
+        <v>-1.2531</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.0385</v>
+        <v>-2.0311</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.0385</v>
+        <v>-1.0311</v>
       </c>
       <c r="G77" t="n">
         <v>-1</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.0385</v>
+        <v>-1.0311</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.0434</v>
+        <v>-1.0398</v>
       </c>
       <c r="J77" t="n">
         <v>-1</v>
@@ -3979,7 +3979,7 @@
         <v>45</v>
       </c>
       <c r="M77" t="n">
-        <v>-2.0434</v>
+        <v>-2.0398</v>
       </c>
       <c r="N77" t="n">
         <v>228</v>
@@ -3998,7 +3998,7 @@
         <v>-1.467</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3421</v>
+        <v>-1.3519</v>
       </c>
       <c r="E78" t="n">
         <v>-2.2791</v>
@@ -4044,7 +4044,7 @@
         <v>-2.044</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.7042</v>
+        <v>-1.709</v>
       </c>
       <c r="E79" t="n">
         <v>-3.1755</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-4.7073</v>
+        <v>-4.6935</v>
       </c>
       <c r="C80" t="n">
-        <v>-3.0299</v>
+        <v>-3.021</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.323</v>
+        <v>-2.3138</v>
       </c>
       <c r="E80" t="n">
-        <v>-4.7073</v>
+        <v>-4.6935</v>
       </c>
       <c r="F80" t="n">
-        <v>-3.7073</v>
+        <v>-3.6935</v>
       </c>
       <c r="G80" t="n">
         <v>-1</v>
       </c>
       <c r="H80" t="n">
-        <v>-3.7073</v>
+        <v>-3.6935</v>
       </c>
       <c r="I80" t="n">
         <v>-3.7246</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-5.1939</v>
+        <v>-5.1795</v>
       </c>
       <c r="C81" t="n">
-        <v>-3.3431</v>
+        <v>-3.3339</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.5196</v>
+        <v>-2.5074</v>
       </c>
       <c r="E81" t="n">
-        <v>-5.1939</v>
+        <v>-5.1795</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.8595</v>
+        <v>-3.8451</v>
       </c>
       <c r="G81" t="n">
         <v>-1.3344</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.8595</v>
+        <v>-3.8451</v>
       </c>
       <c r="I81" t="n">
         <v>-3.8775</v>

--- a/database/event/8042/event_8042_evp_summary.xlsx
+++ b/database/event/8042/event_8042_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.3348</v>
+        <v>9.718</v>
       </c>
       <c r="C2" t="n">
-        <v>6.0085</v>
+        <v>6.2551</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6252</v>
+        <v>3.727</v>
       </c>
       <c r="E2" t="n">
-        <v>9.3348</v>
+        <v>9.718</v>
       </c>
       <c r="F2" t="n">
-        <v>3.144</v>
+        <v>3.1442</v>
       </c>
       <c r="G2" t="n">
         <v>6.1908</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1564</v>
+        <v>4.1567</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1564</v>
+        <v>4.1567</v>
       </c>
       <c r="J2" t="n">
-        <v>6.8351</v>
+        <v>6.8355</v>
       </c>
       <c r="K2" t="n">
         <v>100</v>
@@ -529,7 +529,7 @@
         <v>164</v>
       </c>
       <c r="M2" t="n">
-        <v>10.9915</v>
+        <v>10.9922</v>
       </c>
       <c r="N2" t="n">
         <v>264</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.6837</v>
+        <v>8.8751</v>
       </c>
       <c r="C3" t="n">
-        <v>5.5894</v>
+        <v>5.7126</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3288</v>
+        <v>3.3505</v>
       </c>
       <c r="E3" t="n">
-        <v>8.6837</v>
+        <v>8.8751</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1408</v>
+        <v>3.141</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5429</v>
+        <v>5.5431</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1492</v>
+        <v>4.1497</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1492</v>
+        <v>4.1497</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5429</v>
+        <v>5.5431</v>
       </c>
       <c r="K3" t="n">
         <v>100</v>
@@ -575,7 +575,7 @@
         <v>164</v>
       </c>
       <c r="M3" t="n">
-        <v>9.6921</v>
+        <v>9.6928</v>
       </c>
       <c r="N3" t="n">
         <v>264</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.0699</v>
+        <v>7.6792</v>
       </c>
       <c r="C4" t="n">
-        <v>4.5507</v>
+        <v>4.9428</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5942</v>
+        <v>2.8163</v>
       </c>
       <c r="E4" t="n">
-        <v>7.0699</v>
+        <v>7.6792</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2537</v>
+        <v>4.2485</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8162</v>
+        <v>2.8157</v>
       </c>
       <c r="H4" t="n">
-        <v>6.5851</v>
+        <v>6.5737</v>
       </c>
       <c r="I4" t="n">
-        <v>6.5851</v>
+        <v>6.5737</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8162</v>
+        <v>2.8157</v>
       </c>
       <c r="K4" t="n">
         <v>104</v>
@@ -621,7 +621,7 @@
         <v>102</v>
       </c>
       <c r="M4" t="n">
-        <v>9.401299999999999</v>
+        <v>9.3894</v>
       </c>
       <c r="N4" t="n">
         <v>206</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.0551</v>
+        <v>7.124</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5411</v>
+        <v>4.5855</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5874</v>
+        <v>2.5683</v>
       </c>
       <c r="E5" t="n">
-        <v>7.0551</v>
+        <v>7.124</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4147</v>
+        <v>2.4057</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6404</v>
+        <v>4.6408</v>
       </c>
       <c r="H5" t="n">
-        <v>2.56</v>
+        <v>2.5405</v>
       </c>
       <c r="I5" t="n">
-        <v>2.56</v>
+        <v>2.5405</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6404</v>
+        <v>4.6408</v>
       </c>
       <c r="K5" t="n">
         <v>100</v>
@@ -667,7 +667,7 @@
         <v>164</v>
       </c>
       <c r="M5" t="n">
-        <v>7.2004</v>
+        <v>7.1813</v>
       </c>
       <c r="N5" t="n">
         <v>264</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.4531</v>
+        <v>6.5957</v>
       </c>
       <c r="C6" t="n">
-        <v>4.1536</v>
+        <v>4.2454</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3134</v>
+        <v>2.3323</v>
       </c>
       <c r="E6" t="n">
-        <v>6.4531</v>
+        <v>6.5957</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5096</v>
+        <v>2.5094</v>
       </c>
       <c r="G6" t="n">
-        <v>3.9435</v>
+        <v>3.9438</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7679</v>
+        <v>2.7674</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8392</v>
+        <v>2.8387</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9435</v>
+        <v>3.9438</v>
       </c>
       <c r="K6" t="n">
         <v>143</v>
@@ -713,7 +713,7 @@
         <v>174</v>
       </c>
       <c r="M6" t="n">
-        <v>6.7827</v>
+        <v>6.7825</v>
       </c>
       <c r="N6" t="n">
         <v>317</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.1176</v>
+        <v>6.2934</v>
       </c>
       <c r="C7" t="n">
-        <v>3.9377</v>
+        <v>4.0508</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1607</v>
+        <v>2.1973</v>
       </c>
       <c r="E7" t="n">
-        <v>6.1176</v>
+        <v>6.2934</v>
       </c>
       <c r="F7" t="n">
         <v>3.6173</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5003</v>
+        <v>2.5006</v>
       </c>
       <c r="H7" t="n">
         <v>5.1923</v>
@@ -750,7 +750,7 @@
         <v>5.1923</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5003</v>
+        <v>2.5006</v>
       </c>
       <c r="K7" t="n">
         <v>150</v>
@@ -759,7 +759,7 @@
         <v>126</v>
       </c>
       <c r="M7" t="n">
-        <v>7.692600000000001</v>
+        <v>7.6929</v>
       </c>
       <c r="N7" t="n">
         <v>276</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.9125</v>
+        <v>5.9556</v>
       </c>
       <c r="C8" t="n">
-        <v>3.8057</v>
+        <v>3.8334</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0673</v>
+        <v>2.0464</v>
       </c>
       <c r="E8" t="n">
-        <v>5.9125</v>
+        <v>5.9556</v>
       </c>
       <c r="F8" t="n">
         <v>2.2975</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6151</v>
+        <v>3.6152</v>
       </c>
       <c r="H8" t="n">
         <v>2.3035</v>
@@ -796,7 +796,7 @@
         <v>2.3035</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6151</v>
+        <v>3.6152</v>
       </c>
       <c r="K8" t="n">
         <v>150</v>
@@ -805,7 +805,7 @@
         <v>126</v>
       </c>
       <c r="M8" t="n">
-        <v>5.9186</v>
+        <v>5.9187</v>
       </c>
       <c r="N8" t="n">
         <v>276</v>
@@ -814,127 +814,127 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.088</v>
+        <v>5.2639</v>
       </c>
       <c r="C9" t="n">
-        <v>3.275</v>
+        <v>3.3882</v>
       </c>
       <c r="D9" t="n">
-        <v>1.692</v>
+        <v>1.7374</v>
       </c>
       <c r="E9" t="n">
-        <v>5.088</v>
+        <v>5.2639</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8478</v>
+        <v>3.2829</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2402</v>
+        <v>1.8009</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8478</v>
+        <v>4.4603</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8954</v>
+        <v>4.4603</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2402</v>
+        <v>1.8009</v>
       </c>
       <c r="K9" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="L9" t="n">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="M9" t="n">
-        <v>5.1356</v>
+        <v>6.261200000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>317</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.0837</v>
+        <v>5.165</v>
       </c>
       <c r="C10" t="n">
-        <v>3.2722</v>
+        <v>3.3245</v>
       </c>
       <c r="D10" t="n">
-        <v>1.69</v>
+        <v>1.6933</v>
       </c>
       <c r="E10" t="n">
-        <v>5.0837</v>
+        <v>5.165</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2829</v>
+        <v>2.6529</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8008</v>
+        <v>2.4076</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4603</v>
+        <v>3.0815</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4603</v>
+        <v>3.1609</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8008</v>
+        <v>2.4076</v>
       </c>
       <c r="K10" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="L10" t="n">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="M10" t="n">
-        <v>6.2611</v>
+        <v>5.5685</v>
       </c>
       <c r="N10" t="n">
-        <v>276</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.06</v>
+        <v>5.1621</v>
       </c>
       <c r="C11" t="n">
-        <v>3.2569</v>
+        <v>3.3227</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6792</v>
+        <v>1.692</v>
       </c>
       <c r="E11" t="n">
-        <v>5.06</v>
+        <v>5.1621</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6531</v>
+        <v>1.8474</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4069</v>
+        <v>3.2407</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0819</v>
+        <v>1.8474</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1613</v>
+        <v>1.895</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4069</v>
+        <v>3.2407</v>
       </c>
       <c r="K11" t="n">
         <v>143</v>
@@ -943,7 +943,7 @@
         <v>174</v>
       </c>
       <c r="M11" t="n">
-        <v>5.5682</v>
+        <v>5.1357</v>
       </c>
       <c r="N11" t="n">
         <v>317</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.3911</v>
+        <v>4.6658</v>
       </c>
       <c r="C12" t="n">
-        <v>2.8264</v>
+        <v>3.0032</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3747</v>
+        <v>1.4703</v>
       </c>
       <c r="E12" t="n">
-        <v>4.3911</v>
+        <v>4.6658</v>
       </c>
       <c r="F12" t="n">
-        <v>3.9462</v>
+        <v>3.9463</v>
       </c>
       <c r="G12" t="n">
         <v>0.4449</v>
       </c>
       <c r="H12" t="n">
-        <v>5.9121</v>
+        <v>5.9123</v>
       </c>
       <c r="I12" t="n">
-        <v>6.0644</v>
+        <v>6.0646</v>
       </c>
       <c r="J12" t="n">
         <v>0.4449</v>
@@ -989,7 +989,7 @@
         <v>45</v>
       </c>
       <c r="M12" t="n">
-        <v>6.5093</v>
+        <v>6.5095</v>
       </c>
       <c r="N12" t="n">
         <v>228</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.7134</v>
+        <v>3.8707</v>
       </c>
       <c r="C13" t="n">
-        <v>2.3902</v>
+        <v>2.4914</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0662</v>
+        <v>1.1151</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7134</v>
+        <v>3.8707</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9098</v>
+        <v>3.2816</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8036</v>
+        <v>0.3733</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6436</v>
+        <v>4.4574</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6436</v>
+        <v>4.4574</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8036</v>
+        <v>0.3733</v>
       </c>
       <c r="K13" t="n">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="L13" t="n">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4472</v>
+        <v>4.8307</v>
       </c>
       <c r="N13" t="n">
-        <v>206</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.6449</v>
+        <v>3.8081</v>
       </c>
       <c r="C14" t="n">
-        <v>2.3461</v>
+        <v>2.4511</v>
       </c>
       <c r="D14" t="n">
-        <v>1.035</v>
+        <v>1.0872</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6449</v>
+        <v>3.8081</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2816</v>
+        <v>2.9099</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3633</v>
+        <v>0.8036</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4574</v>
+        <v>3.6439</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4574</v>
+        <v>3.6439</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3633</v>
+        <v>0.8036</v>
       </c>
       <c r="K14" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="L14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="M14" t="n">
-        <v>4.8207</v>
+        <v>4.4475</v>
       </c>
       <c r="N14" t="n">
-        <v>138</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.5563</v>
+        <v>3.7876</v>
       </c>
       <c r="C15" t="n">
-        <v>2.2891</v>
+        <v>2.4379</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9947</v>
+        <v>1.078</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5563</v>
+        <v>3.7876</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4784</v>
+        <v>2.4785</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0779</v>
+        <v>1.1014</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6996</v>
+        <v>2.6998</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6996</v>
+        <v>2.6998</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0779</v>
+        <v>1.1014</v>
       </c>
       <c r="K15" t="n">
         <v>108</v>
@@ -1127,7 +1127,7 @@
         <v>35</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7775</v>
+        <v>3.8012</v>
       </c>
       <c r="N15" t="n">
         <v>143</v>
@@ -1136,277 +1136,277 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.3703</v>
+        <v>3.6961</v>
       </c>
       <c r="C16" t="n">
-        <v>2.1693</v>
+        <v>2.3791</v>
       </c>
       <c r="D16" t="n">
-        <v>0.91</v>
+        <v>1.0371</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3703</v>
+        <v>3.6961</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1041</v>
+        <v>3.3807</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2662</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4.069</v>
+        <v>4.6744</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1739</v>
+        <v>4.6744</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2662</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="L16" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.440099999999999</v>
+        <v>4.6744</v>
       </c>
       <c r="N16" t="n">
-        <v>228</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.3575</v>
+        <v>3.6593</v>
       </c>
       <c r="C17" t="n">
-        <v>2.1611</v>
+        <v>2.3554</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9042</v>
+        <v>1.0207</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3575</v>
+        <v>3.6593</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3575</v>
+        <v>3.1042</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.2662</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6235</v>
+        <v>4.0692</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6235</v>
+        <v>4.1741</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.2662</v>
       </c>
       <c r="K17" t="n">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6235</v>
+        <v>4.440300000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>147</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>Kvem</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.356</v>
+        <v>3.5459</v>
       </c>
       <c r="C18" t="n">
-        <v>2.1601</v>
+        <v>2.2824</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9035</v>
+        <v>0.9701</v>
       </c>
       <c r="E18" t="n">
-        <v>3.356</v>
+        <v>3.5459</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0259</v>
+        <v>3.3003</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3301</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0259</v>
+        <v>4.4984</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0259</v>
+        <v>4.4984</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3301</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="L18" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.356</v>
+        <v>4.4984</v>
       </c>
       <c r="N18" t="n">
-        <v>264</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kvem</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.3058</v>
+        <v>3.4283</v>
       </c>
       <c r="C19" t="n">
-        <v>2.1278</v>
+        <v>2.2067</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8807</v>
+        <v>0.9175</v>
       </c>
       <c r="E19" t="n">
-        <v>3.3058</v>
+        <v>3.4283</v>
       </c>
       <c r="F19" t="n">
-        <v>3.3058</v>
+        <v>3.2334</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.0459</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5105</v>
+        <v>4.352</v>
       </c>
       <c r="I19" t="n">
-        <v>4.5105</v>
+        <v>4.4641</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.0459</v>
       </c>
       <c r="K19" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5105</v>
+        <v>4.51</v>
       </c>
       <c r="N19" t="n">
-        <v>178</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.2793</v>
+        <v>3.2883</v>
       </c>
       <c r="C20" t="n">
-        <v>2.1108</v>
+        <v>2.1166</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8686</v>
+        <v>0.855</v>
       </c>
       <c r="E20" t="n">
-        <v>3.2793</v>
+        <v>3.2883</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2334</v>
+        <v>3.3729</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0459</v>
+        <v>-0.1263</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3519</v>
+        <v>4.6573</v>
       </c>
       <c r="I20" t="n">
-        <v>4.464</v>
+        <v>4.7773</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0459</v>
+        <v>-0.1263</v>
       </c>
       <c r="K20" t="n">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="L20" t="n">
-        <v>45</v>
+        <v>174</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5099</v>
+        <v>4.651000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>228</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.2697</v>
+        <v>3.2069</v>
       </c>
       <c r="C21" t="n">
-        <v>2.1046</v>
+        <v>2.0642</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8642</v>
+        <v>0.8186</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2697</v>
+        <v>3.2069</v>
       </c>
       <c r="F21" t="n">
-        <v>3.3668</v>
+        <v>1.0263</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.09710000000000001</v>
+        <v>2.3157</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6439</v>
+        <v>1.0263</v>
       </c>
       <c r="I21" t="n">
-        <v>4.7636</v>
+        <v>1.0263</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.09710000000000001</v>
+        <v>2.3157</v>
       </c>
       <c r="K21" t="n">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="M21" t="n">
-        <v>4.6665</v>
+        <v>3.342</v>
       </c>
       <c r="N21" t="n">
-        <v>317</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.1013</v>
+        <v>3.1799</v>
       </c>
       <c r="C22" t="n">
-        <v>1.9962</v>
+        <v>2.0468</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7876</v>
+        <v>0.8066</v>
       </c>
       <c r="E22" t="n">
-        <v>3.1013</v>
+        <v>3.1799</v>
       </c>
       <c r="F22" t="n">
-        <v>3.1013</v>
+        <v>3.1109</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>4.0629</v>
+        <v>4.0839</v>
       </c>
       <c r="I22" t="n">
-        <v>4.0629</v>
+        <v>4.0839</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.0629</v>
+        <v>4.0839</v>
       </c>
       <c r="N22" t="n">
         <v>178</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.9783</v>
+        <v>3.1701</v>
       </c>
       <c r="C23" t="n">
-        <v>1.917</v>
+        <v>2.0405</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7316</v>
+        <v>0.8022</v>
       </c>
       <c r="E23" t="n">
-        <v>2.9783</v>
+        <v>3.1701</v>
       </c>
       <c r="F23" t="n">
-        <v>3.0932</v>
+        <v>3.093</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1149</v>
+        <v>-0.1153</v>
       </c>
       <c r="H23" t="n">
-        <v>4.0452</v>
+        <v>4.0447</v>
       </c>
       <c r="I23" t="n">
-        <v>4.1494</v>
+        <v>4.1489</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1149</v>
+        <v>-0.1153</v>
       </c>
       <c r="K23" t="n">
         <v>180</v>
@@ -1495,7 +1495,7 @@
         <v>39</v>
       </c>
       <c r="M23" t="n">
-        <v>4.0345</v>
+        <v>4.0336</v>
       </c>
       <c r="N23" t="n">
         <v>219</v>
@@ -1504,35 +1504,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.7861</v>
+        <v>2.7693</v>
       </c>
       <c r="C24" t="n">
-        <v>1.7933</v>
+        <v>1.7825</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6441</v>
+        <v>0.6232</v>
       </c>
       <c r="E24" t="n">
-        <v>2.7861</v>
+        <v>2.7693</v>
       </c>
       <c r="F24" t="n">
-        <v>2.243</v>
+        <v>3.0943</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5431</v>
+        <v>-0.3036</v>
       </c>
       <c r="H24" t="n">
-        <v>2.243</v>
+        <v>4.0476</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3008</v>
+        <v>4.1519</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5431</v>
+        <v>-0.3036</v>
       </c>
       <c r="K24" t="n">
         <v>180</v>
@@ -1541,7 +1541,7 @@
         <v>39</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8439</v>
+        <v>3.8483</v>
       </c>
       <c r="N24" t="n">
         <v>219</v>
@@ -1550,35 +1550,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.7783</v>
+        <v>2.722</v>
       </c>
       <c r="C25" t="n">
-        <v>1.7883</v>
+        <v>1.7521</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6405</v>
+        <v>0.602</v>
       </c>
       <c r="E25" t="n">
-        <v>2.7783</v>
+        <v>2.722</v>
       </c>
       <c r="F25" t="n">
-        <v>3.0944</v>
+        <v>2.2429</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3161</v>
+        <v>0.5429</v>
       </c>
       <c r="H25" t="n">
-        <v>4.0478</v>
+        <v>2.2429</v>
       </c>
       <c r="I25" t="n">
-        <v>4.1521</v>
+        <v>2.3007</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3161</v>
+        <v>0.5429</v>
       </c>
       <c r="K25" t="n">
         <v>180</v>
@@ -1587,7 +1587,7 @@
         <v>39</v>
       </c>
       <c r="M25" t="n">
-        <v>3.836</v>
+        <v>2.8436</v>
       </c>
       <c r="N25" t="n">
         <v>219</v>
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.4243</v>
+        <v>2.6248</v>
       </c>
       <c r="C26" t="n">
-        <v>1.5604</v>
+        <v>1.6895</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4794</v>
+        <v>0.5586</v>
       </c>
       <c r="E26" t="n">
-        <v>2.4243</v>
+        <v>2.6248</v>
       </c>
       <c r="F26" t="n">
         <v>3.0992</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.6753</v>
       </c>
       <c r="H26" t="n">
         <v>4.0583</v>
@@ -1624,7 +1624,7 @@
         <v>4.0583</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.6753</v>
       </c>
       <c r="K26" t="n">
         <v>75</v>
@@ -1633,7 +1633,7 @@
         <v>63</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3834</v>
+        <v>3.383</v>
       </c>
       <c r="N26" t="n">
         <v>138</v>
@@ -1642,185 +1642,185 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>try</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.4023</v>
+        <v>2.6001</v>
       </c>
       <c r="C27" t="n">
-        <v>1.5463</v>
+        <v>1.6736</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4694</v>
+        <v>0.5476</v>
       </c>
       <c r="E27" t="n">
-        <v>2.4023</v>
+        <v>2.6001</v>
       </c>
       <c r="F27" t="n">
-        <v>2.4023</v>
+        <v>2.2708</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.5329</v>
+        <v>2.2708</v>
       </c>
       <c r="I27" t="n">
-        <v>2.5329</v>
+        <v>2.2708</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.5329</v>
+        <v>2.2708</v>
       </c>
       <c r="N27" t="n">
-        <v>181</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>try</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.2543</v>
+        <v>2.263</v>
       </c>
       <c r="C28" t="n">
-        <v>1.451</v>
+        <v>1.4566</v>
       </c>
       <c r="D28" t="n">
-        <v>0.402</v>
+        <v>0.397</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2543</v>
+        <v>2.263</v>
       </c>
       <c r="F28" t="n">
-        <v>2.2543</v>
+        <v>2.3971</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.2543</v>
+        <v>2.5215</v>
       </c>
       <c r="I28" t="n">
-        <v>2.2543</v>
+        <v>2.5215</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>106</v>
+        <v>181</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.2543</v>
+        <v>2.5215</v>
       </c>
       <c r="N28" t="n">
-        <v>106</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.0403</v>
+        <v>2.0795</v>
       </c>
       <c r="C29" t="n">
-        <v>1.3133</v>
+        <v>1.3385</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3046</v>
+        <v>0.315</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0403</v>
+        <v>2.0795</v>
       </c>
       <c r="F29" t="n">
-        <v>2.0403</v>
+        <v>1.6035</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.0403</v>
+        <v>1.6035</v>
       </c>
       <c r="I29" t="n">
-        <v>2.0403</v>
+        <v>1.6035</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.0403</v>
+        <v>1.6035</v>
       </c>
       <c r="N29" t="n">
-        <v>181</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.9348</v>
+        <v>2.055</v>
       </c>
       <c r="C30" t="n">
-        <v>1.2454</v>
+        <v>1.3227</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2566</v>
+        <v>0.3041</v>
       </c>
       <c r="E30" t="n">
-        <v>1.9348</v>
+        <v>2.055</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6503</v>
+        <v>2.0402</v>
       </c>
       <c r="G30" t="n">
-        <v>1.2845</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6503</v>
+        <v>2.0402</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6503</v>
+        <v>2.0402</v>
       </c>
       <c r="J30" t="n">
-        <v>1.2845</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="L30" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.9348</v>
+        <v>2.0402</v>
       </c>
       <c r="N30" t="n">
-        <v>276</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.9257</v>
+        <v>2.0022</v>
       </c>
       <c r="C31" t="n">
-        <v>1.2395</v>
+        <v>1.2887</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2524</v>
+        <v>0.2805</v>
       </c>
       <c r="E31" t="n">
-        <v>1.9257</v>
+        <v>2.0022</v>
       </c>
       <c r="F31" t="n">
-        <v>2.1359</v>
+        <v>2.1363</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.2102</v>
+        <v>-0.2106</v>
       </c>
       <c r="H31" t="n">
-        <v>2.1359</v>
+        <v>2.1363</v>
       </c>
       <c r="I31" t="n">
-        <v>2.1359</v>
+        <v>2.1363</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.2102</v>
+        <v>-0.2106</v>
       </c>
       <c r="K31" t="n">
         <v>108</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.8484</v>
+        <v>1.9939</v>
       </c>
       <c r="C32" t="n">
-        <v>1.1898</v>
+        <v>1.2834</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2172</v>
+        <v>0.2768</v>
       </c>
       <c r="E32" t="n">
-        <v>1.8484</v>
+        <v>1.9939</v>
       </c>
       <c r="F32" t="n">
-        <v>2.8484</v>
+        <v>2.8485</v>
       </c>
       <c r="G32" t="n">
         <v>-1</v>
       </c>
       <c r="H32" t="n">
-        <v>3.5093</v>
+        <v>3.5096</v>
       </c>
       <c r="I32" t="n">
-        <v>3.5093</v>
+        <v>3.5096</v>
       </c>
       <c r="J32" t="n">
         <v>-1</v>
@@ -1909,7 +1909,7 @@
         <v>35</v>
       </c>
       <c r="M32" t="n">
-        <v>2.5093</v>
+        <v>2.5096</v>
       </c>
       <c r="N32" t="n">
         <v>143</v>
@@ -1918,81 +1918,81 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.8276</v>
+        <v>1.9572</v>
       </c>
       <c r="C33" t="n">
-        <v>1.1764</v>
+        <v>1.2598</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2078</v>
+        <v>0.2604</v>
       </c>
       <c r="E33" t="n">
-        <v>1.8276</v>
+        <v>1.9572</v>
       </c>
       <c r="F33" t="n">
-        <v>2.2763</v>
+        <v>0.6503</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4487</v>
+        <v>1.2706</v>
       </c>
       <c r="H33" t="n">
-        <v>2.2763</v>
+        <v>0.6503</v>
       </c>
       <c r="I33" t="n">
-        <v>2.2763</v>
+        <v>0.6503</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4487</v>
+        <v>1.2706</v>
       </c>
       <c r="K33" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L33" t="n">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="M33" t="n">
-        <v>1.8276</v>
+        <v>1.9209</v>
       </c>
       <c r="N33" t="n">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.7633</v>
+        <v>1.6879</v>
       </c>
       <c r="C34" t="n">
-        <v>1.135</v>
+        <v>1.0864</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1785</v>
+        <v>0.1401</v>
       </c>
       <c r="E34" t="n">
-        <v>1.7633</v>
+        <v>1.6879</v>
       </c>
       <c r="F34" t="n">
-        <v>2.1797</v>
+        <v>2.2763</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.4164</v>
+        <v>-0.4492</v>
       </c>
       <c r="H34" t="n">
-        <v>2.1797</v>
+        <v>2.2763</v>
       </c>
       <c r="I34" t="n">
-        <v>2.1797</v>
+        <v>2.2763</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.4164</v>
+        <v>-0.4492</v>
       </c>
       <c r="K34" t="n">
         <v>75</v>
@@ -2001,7 +2001,7 @@
         <v>63</v>
       </c>
       <c r="M34" t="n">
-        <v>1.7633</v>
+        <v>1.8271</v>
       </c>
       <c r="N34" t="n">
         <v>138</v>
@@ -2010,47 +2010,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.6037</v>
+        <v>1.6868</v>
       </c>
       <c r="C35" t="n">
-        <v>1.0322</v>
+        <v>1.0857</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1058</v>
+        <v>0.1396</v>
       </c>
       <c r="E35" t="n">
-        <v>1.6037</v>
+        <v>1.6868</v>
       </c>
       <c r="F35" t="n">
-        <v>1.6037</v>
+        <v>2.1797</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.4168</v>
       </c>
       <c r="H35" t="n">
-        <v>1.6037</v>
+        <v>2.1797</v>
       </c>
       <c r="I35" t="n">
-        <v>1.6037</v>
+        <v>2.1797</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.4168</v>
       </c>
       <c r="K35" t="n">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M35" t="n">
-        <v>1.6037</v>
+        <v>1.7629</v>
       </c>
       <c r="N35" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36">
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.4893</v>
+        <v>1.5248</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9586</v>
+        <v>0.9815</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0538</v>
+        <v>0.0673</v>
       </c>
       <c r="E36" t="n">
-        <v>1.4893</v>
+        <v>1.5248</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3754</v>
+        <v>1.3539</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1139</v>
+        <v>0.1127</v>
       </c>
       <c r="H36" t="n">
-        <v>1.3754</v>
+        <v>1.3539</v>
       </c>
       <c r="I36" t="n">
-        <v>1.3754</v>
+        <v>1.3539</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1139</v>
+        <v>0.1127</v>
       </c>
       <c r="K36" t="n">
         <v>108</v>
@@ -2093,7 +2093,7 @@
         <v>35</v>
       </c>
       <c r="M36" t="n">
-        <v>1.4893</v>
+        <v>1.4666</v>
       </c>
       <c r="N36" t="n">
         <v>143</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.4196</v>
+        <v>1.5196</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9137</v>
+        <v>0.9781</v>
       </c>
       <c r="D37" t="n">
-        <v>0.022</v>
+        <v>0.065</v>
       </c>
       <c r="E37" t="n">
-        <v>1.4196</v>
+        <v>1.5196</v>
       </c>
       <c r="F37" t="n">
-        <v>2.0823</v>
+        <v>2.0822</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6627</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>2.0823</v>
+        <v>2.0822</v>
       </c>
       <c r="I37" t="n">
-        <v>2.136</v>
+        <v>2.1359</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6627</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="K37" t="n">
         <v>180</v>
@@ -2139,7 +2139,7 @@
         <v>39</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4733</v>
+        <v>1.4731</v>
       </c>
       <c r="N37" t="n">
         <v>219</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>xiELO</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.3948</v>
+        <v>1.4511</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8978</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0107</v>
+        <v>0.0344</v>
       </c>
       <c r="E38" t="n">
-        <v>1.3948</v>
+        <v>1.4511</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3948</v>
+        <v>1.3024</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.3948</v>
+        <v>1.3024</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3948</v>
+        <v>1.3024</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>181</v>
+        <v>119</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3948</v>
+        <v>1.3024</v>
       </c>
       <c r="N38" t="n">
-        <v>181</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>xiELO</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.3022</v>
+        <v>1.3675</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.8802</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0314</v>
+        <v>-0.003</v>
       </c>
       <c r="E39" t="n">
-        <v>1.3022</v>
+        <v>1.3675</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3022</v>
+        <v>1.3948</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.3022</v>
+        <v>1.3948</v>
       </c>
       <c r="I39" t="n">
-        <v>1.3022</v>
+        <v>1.3948</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.3022</v>
+        <v>1.3948</v>
       </c>
       <c r="N39" t="n">
-        <v>119</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.266</v>
+        <v>1.282</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8149</v>
+        <v>0.8252</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0479</v>
+        <v>-0.0412</v>
       </c>
       <c r="E40" t="n">
-        <v>1.266</v>
+        <v>1.282</v>
       </c>
       <c r="F40" t="n">
-        <v>1.266</v>
+        <v>1.2814</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.266</v>
+        <v>1.2814</v>
       </c>
       <c r="I40" t="n">
-        <v>1.266</v>
+        <v>1.2814</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.266</v>
+        <v>1.2814</v>
       </c>
       <c r="N40" t="n">
         <v>147</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.228</v>
+        <v>1.1741</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7904</v>
+        <v>0.7557</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>1.228</v>
+        <v>1.1741</v>
       </c>
       <c r="F41" t="n">
-        <v>1.228</v>
+        <v>1.2373</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.228</v>
+        <v>1.2373</v>
       </c>
       <c r="I41" t="n">
-        <v>1.228</v>
+        <v>1.2373</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.228</v>
+        <v>1.2373</v>
       </c>
       <c r="N41" t="n">
         <v>127</v>
@@ -2336,16 +2336,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.1181</v>
+        <v>1.1559</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7197</v>
+        <v>0.744</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1152</v>
+        <v>-0.0975</v>
       </c>
       <c r="E42" t="n">
-        <v>1.1181</v>
+        <v>1.1559</v>
       </c>
       <c r="F42" t="n">
         <v>1.1181</v>
@@ -2378,78 +2378,78 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>kensizor</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.995</v>
+        <v>1.0759</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6404</v>
+        <v>0.6925</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1713</v>
+        <v>-0.1332</v>
       </c>
       <c r="E43" t="n">
-        <v>0.995</v>
+        <v>1.0759</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.3934</v>
+        <v>0.9435</v>
       </c>
       <c r="G43" t="n">
-        <v>1.3884</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.3934</v>
+        <v>0.9435</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.3934</v>
+        <v>0.9435</v>
       </c>
       <c r="J43" t="n">
-        <v>1.3884</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="L43" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.9435</v>
       </c>
       <c r="N43" t="n">
-        <v>206</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kensizor</t>
+          <t>esenthial</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9435</v>
+        <v>0.9617</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6073</v>
+        <v>0.619</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1947</v>
+        <v>-0.1842</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9435</v>
+        <v>0.9617</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9435</v>
+        <v>0.8838</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9435</v>
+        <v>0.8838</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9435</v>
+        <v>0.8838</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.9435</v>
+        <v>0.8838</v>
       </c>
       <c r="N44" t="n">
         <v>167</v>
@@ -2470,47 +2470,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>esenthial</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8838</v>
+        <v>0.9173</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5689</v>
+        <v>0.5904</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2219</v>
+        <v>-0.2041</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8838</v>
+        <v>0.9173</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8838</v>
+        <v>-0.4528</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1.4005</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8838</v>
+        <v>-0.4528</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8838</v>
+        <v>-0.4528</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1.4005</v>
       </c>
       <c r="K45" t="n">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M45" t="n">
-        <v>0.8838</v>
+        <v>0.9477000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>167</v>
+        <v>206</v>
       </c>
     </row>
     <row r="46">
@@ -2520,28 +2520,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8043</v>
+        <v>0.5563</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5177</v>
+        <v>0.3581</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2581</v>
+        <v>-0.3653</v>
       </c>
       <c r="E46" t="n">
-        <v>0.8043</v>
+        <v>0.5563</v>
       </c>
       <c r="F46" t="n">
-        <v>1.4589</v>
+        <v>1.4552</v>
       </c>
       <c r="G46" t="n">
         <v>-0.6546</v>
       </c>
       <c r="H46" t="n">
-        <v>1.4589</v>
+        <v>1.4552</v>
       </c>
       <c r="I46" t="n">
-        <v>1.4965</v>
+        <v>1.4927</v>
       </c>
       <c r="J46" t="n">
         <v>-0.6546</v>
@@ -2553,7 +2553,7 @@
         <v>45</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8419</v>
+        <v>0.8381</v>
       </c>
       <c r="N46" t="n">
         <v>228</v>
@@ -2566,31 +2566,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5843</v>
+        <v>0.4735</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3761</v>
+        <v>0.3048</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3582</v>
+        <v>-0.4023</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5843</v>
+        <v>0.4735</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.5402</v>
+        <v>-1.5398</v>
       </c>
       <c r="G47" t="n">
-        <v>2.1245</v>
+        <v>2.1159</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.5402</v>
+        <v>-1.5398</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.5402</v>
+        <v>-1.5398</v>
       </c>
       <c r="J47" t="n">
-        <v>2.1245</v>
+        <v>2.1159</v>
       </c>
       <c r="K47" t="n">
         <v>104</v>
@@ -2599,7 +2599,7 @@
         <v>102</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5842999999999998</v>
+        <v>0.5760999999999998</v>
       </c>
       <c r="N47" t="n">
         <v>206</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5602</v>
+        <v>0.4412</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3606</v>
+        <v>0.284</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3692</v>
+        <v>-0.4167</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5602</v>
+        <v>0.4412</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5602</v>
+        <v>0.5596</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5602</v>
+        <v>0.5596</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5602</v>
+        <v>0.5596</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5602</v>
+        <v>0.5596</v>
       </c>
       <c r="N48" t="n">
         <v>90</v>
@@ -2654,139 +2654,139 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4511</v>
+        <v>0.3105</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2904</v>
+        <v>0.1999</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4189</v>
+        <v>-0.4751</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4511</v>
+        <v>0.3105</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4511</v>
+        <v>0.3971</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.4511</v>
+        <v>0.3971</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4511</v>
+        <v>0.3971</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4511</v>
+        <v>0.3971</v>
       </c>
       <c r="N49" t="n">
-        <v>147</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4172</v>
+        <v>0.2909</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2685</v>
+        <v>0.1872</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4343</v>
+        <v>-0.4839</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4172</v>
+        <v>0.2909</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4172</v>
+        <v>0.45</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4172</v>
+        <v>0.45</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4172</v>
+        <v>0.45</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4172</v>
+        <v>0.45</v>
       </c>
       <c r="N50" t="n">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0415</v>
+        <v>0.059</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0267</v>
+        <v>0.038</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6052999999999999</v>
+        <v>-0.5875</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0415</v>
+        <v>0.059</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0415</v>
+        <v>0.0073</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0415</v>
+        <v>0.0073</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0415</v>
+        <v>0.0073</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0415</v>
+        <v>0.0073</v>
       </c>
       <c r="N51" t="n">
-        <v>127</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52">
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0023</v>
+        <v>0.0518</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0015</v>
+        <v>0.0333</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6232</v>
+        <v>-0.5907</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0023</v>
+        <v>0.0518</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0023</v>
+        <v>0.002</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0023</v>
+        <v>0.002</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0023</v>
+        <v>0.002</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.0023</v>
+        <v>0.002</v>
       </c>
       <c r="N52" t="n">
         <v>119</v>
@@ -2838,32 +2838,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0081</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0052</v>
+        <v>-0.0525</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6279</v>
+        <v>-0.6503</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0081</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.0081</v>
+        <v>-0.3324</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.0081</v>
+        <v>-0.3324</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0081</v>
+        <v>-0.3324</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.0081</v>
+        <v>-0.3324</v>
       </c>
       <c r="N53" t="n">
         <v>90</v>
@@ -2884,47 +2884,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1611</v>
+        <v>-0.1239</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1037</v>
+        <v>-0.0798</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6975</v>
+        <v>-0.6692</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1611</v>
+        <v>-0.1239</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1611</v>
+        <v>0.0407</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1611</v>
+        <v>0.0407</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1611</v>
+        <v>0.0407</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.1611</v>
+        <v>0.0407</v>
       </c>
       <c r="N54" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55">
@@ -2934,22 +2934,22 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1619</v>
+        <v>-0.308</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1042</v>
+        <v>-0.1982</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6979</v>
+        <v>-0.7514</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1619</v>
+        <v>-0.308</v>
       </c>
       <c r="F55" t="n">
         <v>0.4575</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.6194</v>
+        <v>-0.611</v>
       </c>
       <c r="H55" t="n">
         <v>0.4575</v>
@@ -2958,7 +2958,7 @@
         <v>0.4575</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.6194</v>
+        <v>-0.611</v>
       </c>
       <c r="K55" t="n">
         <v>75</v>
@@ -2967,7 +2967,7 @@
         <v>63</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.1618999999999999</v>
+        <v>-0.1535</v>
       </c>
       <c r="N55" t="n">
         <v>138</v>
@@ -2976,78 +2976,78 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.3322</v>
+        <v>-0.3108</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2138</v>
+        <v>-0.2001</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7754</v>
+        <v>-0.7526</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3322</v>
+        <v>-0.3108</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.3322</v>
+        <v>-0.4275</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.3322</v>
+        <v>-0.4275</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3322</v>
+        <v>-0.4275</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.3322</v>
+        <v>-0.4275</v>
       </c>
       <c r="N56" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BELCHONOKK</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3715</v>
+        <v>-0.3126</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2391</v>
+        <v>-0.2012</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7933</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3715</v>
+        <v>-0.3126</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.3715</v>
+        <v>-0.1614</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.3715</v>
+        <v>-0.1614</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.3715</v>
+        <v>-0.1614</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.3715</v>
+        <v>-0.1614</v>
       </c>
       <c r="N57" t="n">
         <v>119</v>
@@ -3068,231 +3068,231 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>BELCHONOKK</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.427</v>
+        <v>-0.4581</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2748</v>
+        <v>-0.2949</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.8186</v>
+        <v>-0.8184</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.427</v>
+        <v>-0.4581</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.427</v>
+        <v>-0.3716</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.427</v>
+        <v>-0.3716</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.427</v>
+        <v>-0.3716</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.427</v>
+        <v>-0.3716</v>
       </c>
       <c r="N58" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.4279</v>
+        <v>-0.5749</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2754</v>
+        <v>-0.37</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.819</v>
+        <v>-0.8706</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.4279</v>
+        <v>-0.5749</v>
       </c>
       <c r="F59" t="n">
-        <v>1.375</v>
+        <v>-0.4772</v>
       </c>
       <c r="G59" t="n">
-        <v>-1.8029</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1.375</v>
+        <v>-0.4772</v>
       </c>
       <c r="I59" t="n">
-        <v>1.375</v>
+        <v>-0.4772</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.8029</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="L59" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.4278999999999999</v>
+        <v>-0.4772</v>
       </c>
       <c r="N59" t="n">
-        <v>206</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.4771</v>
+        <v>-0.6519</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3071</v>
+        <v>-0.4196</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.8414</v>
+        <v>-0.905</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.4771</v>
+        <v>-0.6519</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.4771</v>
+        <v>-0.6474</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.4771</v>
+        <v>-0.6474</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4771</v>
+        <v>-0.6474</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.4771</v>
+        <v>-0.6474</v>
       </c>
       <c r="N60" t="n">
-        <v>127</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5248</v>
+        <v>-0.7096</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3378</v>
+        <v>-0.4567</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.8631</v>
+        <v>-0.9308</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5248</v>
+        <v>-0.7096</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5248</v>
+        <v>1.3844</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>-1.8031</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5248</v>
+        <v>1.3844</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5248</v>
+        <v>1.3844</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>-1.8031</v>
       </c>
       <c r="K61" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.5248</v>
+        <v>-0.4186999999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>90</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.5456</v>
+        <v>-0.7195</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3512</v>
+        <v>-0.4631</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8726</v>
+        <v>-0.9352</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5456</v>
+        <v>-0.7195</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.1055</v>
+        <v>-0.6157</v>
       </c>
       <c r="G62" t="n">
-        <v>0.5599</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-1.1055</v>
+        <v>-0.6157</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.1055</v>
+        <v>-0.6157</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5599</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="L62" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.5456</v>
+        <v>-0.6157</v>
       </c>
       <c r="N62" t="n">
-        <v>276</v>
+        <v>106</v>
       </c>
     </row>
     <row r="63">
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.5705</v>
+        <v>-0.7447</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3672</v>
+        <v>-0.4793</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8839</v>
+        <v>-0.9465</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5705</v>
+        <v>-0.7447</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.5705</v>
+        <v>-0.5703</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.5705</v>
+        <v>-0.5703</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.5705</v>
+        <v>-0.5703</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.5705</v>
+        <v>-0.5703</v>
       </c>
       <c r="N63" t="n">
         <v>181</v>
@@ -3344,277 +3344,277 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.6283</v>
+        <v>-0.748</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4044</v>
+        <v>-0.4815</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.9102</v>
+        <v>-0.9479</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.6283</v>
+        <v>-0.748</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.6283</v>
+        <v>-0.7571</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.6283</v>
+        <v>-0.7571</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.6283</v>
+        <v>-0.7571</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.6283</v>
+        <v>-0.7571</v>
       </c>
       <c r="N64" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.6313</v>
+        <v>-0.7627</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4063</v>
+        <v>-0.4909</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9116</v>
+        <v>-0.9545</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.6313</v>
+        <v>-0.7627</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.6313</v>
+        <v>-0.525</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.6313</v>
+        <v>-0.525</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.6313</v>
+        <v>-0.525</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.6313</v>
+        <v>-0.525</v>
       </c>
       <c r="N65" t="n">
-        <v>147</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.6474</v>
+        <v>-0.8505</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4167</v>
+        <v>-0.5474</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.9937</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6474</v>
+        <v>-0.8505</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.6474</v>
+        <v>-1.1055</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>0.5601</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.6474</v>
+        <v>-1.1055</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6474</v>
+        <v>-1.1055</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>0.5601</v>
       </c>
       <c r="K66" t="n">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.6474</v>
+        <v>-0.5453999999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>167</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.757</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4873</v>
+        <v>-0.5642</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9688</v>
+        <v>-1.0053</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.757</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.757</v>
+        <v>-0.6322</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.757</v>
+        <v>-0.6322</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.757</v>
+        <v>-0.6322</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.757</v>
+        <v>-0.6322</v>
       </c>
       <c r="N67" t="n">
-        <v>90</v>
+        <v>147</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>noway</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8025</v>
+        <v>-0.9466</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5165</v>
+        <v>-0.6093</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9895</v>
+        <v>-1.0366</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8025</v>
+        <v>-0.9466</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.3916</v>
+        <v>-0.8263</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.4109</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.3916</v>
+        <v>-0.8263</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3916</v>
+        <v>-0.8263</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.4109</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L68" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.8025</v>
+        <v>-0.8263</v>
       </c>
       <c r="N68" t="n">
-        <v>143</v>
+        <v>106</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>noway</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.8254</v>
+        <v>-1.0416</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5313</v>
+        <v>-0.6704</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9999</v>
+        <v>-1.0791</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.8254</v>
+        <v>-1.0416</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.8254</v>
+        <v>-0.3913</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>-0.4113</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.8254</v>
+        <v>-0.3913</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.8254</v>
+        <v>-0.3913</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-0.4113</v>
       </c>
       <c r="K69" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.8254</v>
+        <v>-0.8026</v>
       </c>
       <c r="N69" t="n">
-        <v>106</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70">
@@ -3624,28 +3624,28 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.8738</v>
+        <v>-1.0448</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5624</v>
+        <v>-0.6725</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.022</v>
+        <v>-1.0805</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.8738</v>
+        <v>-1.0448</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.8738</v>
+        <v>-0.8655</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.8738</v>
+        <v>-0.8655</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.8738</v>
+        <v>-0.8655</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.8738</v>
+        <v>-0.8655</v>
       </c>
       <c r="N70" t="n">
         <v>119</v>
@@ -3670,28 +3670,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.8905</v>
+        <v>-1.0618</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5732</v>
+        <v>-0.6834</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0296</v>
+        <v>-1.0881</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.8905</v>
+        <v>-1.0618</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.8905</v>
+        <v>-0.8804</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.8905</v>
+        <v>-0.8804</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8905</v>
+        <v>-0.8804</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.8905</v>
+        <v>-0.8804</v>
       </c>
       <c r="N71" t="n">
         <v>181</v>
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-1.1308</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6206</v>
+        <v>-0.7279</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0631</v>
+        <v>-1.1189</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-1.1308</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.1655</v>
+        <v>-0.166</v>
       </c>
       <c r="G72" t="n">
         <v>-0.7987</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.1655</v>
+        <v>-0.166</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.1698</v>
+        <v>-0.1703</v>
       </c>
       <c r="J72" t="n">
         <v>-0.7987</v>
@@ -3749,7 +3749,7 @@
         <v>45</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9684999999999999</v>
+        <v>-0.969</v>
       </c>
       <c r="N72" t="n">
         <v>228</v>
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.0052</v>
+        <v>-1.2338</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.647</v>
+        <v>-0.7942</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0818</v>
+        <v>-1.1649</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.0052</v>
+        <v>-1.2338</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.0052</v>
+        <v>-1.0048</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.0052</v>
+        <v>-1.0048</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.0052</v>
+        <v>-1.0048</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.0052</v>
+        <v>-1.0048</v>
       </c>
       <c r="N73" t="n">
         <v>178</v>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.0173</v>
+        <v>-1.2686</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6548</v>
+        <v>-0.8166</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0873</v>
+        <v>-1.1805</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0173</v>
+        <v>-1.2686</v>
       </c>
       <c r="F74" t="n">
         <v>-1.0173</v>
@@ -3850,93 +3850,93 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.0551</v>
+        <v>-1.3561</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6791</v>
+        <v>-0.8729</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1045</v>
+        <v>-1.2196</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.0551</v>
+        <v>-1.3561</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.0551</v>
+        <v>-1.2786</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.0551</v>
+        <v>-1.2786</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.0551</v>
+        <v>-1.2786</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.0551</v>
+        <v>-1.2786</v>
       </c>
       <c r="N75" t="n">
-        <v>106</v>
+        <v>178</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.2791</v>
+        <v>-1.4237</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.8233</v>
+        <v>-0.9164</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2065</v>
+        <v>-1.2498</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.2791</v>
+        <v>-1.4237</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.2791</v>
+        <v>-1.0468</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.2791</v>
+        <v>-1.0468</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2791</v>
+        <v>-1.0468</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>178</v>
+        <v>106</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.2791</v>
+        <v>-1.0468</v>
       </c>
       <c r="N76" t="n">
-        <v>178</v>
+        <v>106</v>
       </c>
     </row>
     <row r="77">
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.3242</v>
+        <v>-1.4597</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.9396</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.227</v>
+        <v>-1.2658</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.3242</v>
+        <v>-1.4597</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.3242</v>
+        <v>-1.3252</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.3242</v>
+        <v>-1.3252</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.3242</v>
+        <v>-1.3252</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.3242</v>
+        <v>-1.3252</v>
       </c>
       <c r="N77" t="n">
         <v>147</v>
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.5946</v>
+        <v>-1.8</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.0264</v>
+        <v>-1.1586</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3501</v>
+        <v>-1.4178</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.5946</v>
+        <v>-1.8</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.5946</v>
+        <v>-1.5949</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.5946</v>
+        <v>-1.5949</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.5946</v>
+        <v>-1.5949</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.5946</v>
+        <v>-1.5949</v>
       </c>
       <c r="N78" t="n">
         <v>127</v>
@@ -4038,31 +4038,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.5092</v>
+        <v>-2.8241</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.6151</v>
+        <v>-1.8178</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.7664</v>
+        <v>-1.8753</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.5092</v>
+        <v>-2.8241</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.5262</v>
+        <v>-0.5259</v>
       </c>
       <c r="G79" t="n">
-        <v>-1.983</v>
+        <v>-1.9828</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.5262</v>
+        <v>-0.5259</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5262</v>
+        <v>-0.5259</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.983</v>
+        <v>-1.9828</v>
       </c>
       <c r="K79" t="n">
         <v>100</v>
@@ -4071,7 +4071,7 @@
         <v>164</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.5092</v>
+        <v>-2.5087</v>
       </c>
       <c r="N79" t="n">
         <v>264</v>
@@ -4080,93 +4080,93 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.5898</v>
+        <v>-3.8532</v>
       </c>
       <c r="C80" t="n">
-        <v>-2.3106</v>
+        <v>-2.4802</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.2584</v>
+        <v>-2.335</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.5898</v>
+        <v>-3.8532</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.7987</v>
+        <v>-3.0253</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.7911</v>
+        <v>-0.6093</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.7987</v>
+        <v>-3.0253</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.8708</v>
+        <v>-3.1033</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.7911</v>
+        <v>-0.6093</v>
       </c>
       <c r="K80" t="n">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="L80" t="n">
-        <v>39</v>
+        <v>174</v>
       </c>
       <c r="M80" t="n">
-        <v>-3.6619</v>
+        <v>-3.7126</v>
       </c>
       <c r="N80" t="n">
-        <v>219</v>
+        <v>317</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.6348</v>
+        <v>-3.8625</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.3396</v>
+        <v>-2.4862</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.2788</v>
+        <v>-2.3391</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.6348</v>
+        <v>-3.8625</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.025</v>
+        <v>-2.7885</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.6098</v>
+        <v>-0.7912</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.025</v>
+        <v>-2.7885</v>
       </c>
       <c r="I81" t="n">
-        <v>-3.103</v>
+        <v>-2.8604</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.6098</v>
+        <v>-0.7912</v>
       </c>
       <c r="K81" t="n">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="L81" t="n">
-        <v>174</v>
+        <v>39</v>
       </c>
       <c r="M81" t="n">
-        <v>-3.7128</v>
+        <v>-3.6516</v>
       </c>
       <c r="N81" t="n">
-        <v>317</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -4469,10 +4469,10 @@
         <v>1.56</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.668</v>
       </c>
       <c r="J7" t="n">
-        <v>12.6882</v>
+        <v>12.692</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6088</v>
+        <v>0.609</v>
       </c>
       <c r="J8" t="n">
-        <v>11.5672</v>
+        <v>11.571</v>
       </c>
     </row>
     <row r="9">
@@ -4546,13 +4546,13 @@
         <v>19</v>
       </c>
       <c r="H9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4358</v>
+        <v>0.4255</v>
       </c>
       <c r="J9" t="n">
-        <v>8.280200000000001</v>
+        <v>8.0845</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>1.26</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3605</v>
+        <v>0.3607</v>
       </c>
       <c r="J10" t="n">
-        <v>6.8495</v>
+        <v>6.8533</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.95</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1106</v>
+        <v>-0.1104</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1014</v>
+        <v>-2.0976</v>
       </c>
     </row>
     <row r="12">
@@ -7069,10 +7069,10 @@
         <v>1.54</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8224</v>
+        <v>0.8218</v>
       </c>
       <c r="J72" t="n">
-        <v>29.6064</v>
+        <v>29.5848</v>
       </c>
     </row>
     <row r="73">
@@ -7106,13 +7106,13 @@
         <v>36</v>
       </c>
       <c r="H73" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4852</v>
+        <v>0.497</v>
       </c>
       <c r="J73" t="n">
-        <v>17.4672</v>
+        <v>17.892</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>0.92</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1233</v>
+        <v>-0.1235</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.4388</v>
+        <v>-4.446</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>0.75</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3006</v>
+        <v>-0.3008</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.8216</v>
+        <v>-10.8288</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>0.53</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4972</v>
+        <v>-0.4974</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.8992</v>
+        <v>-17.9064</v>
       </c>
     </row>
     <row r="77">
@@ -7669,10 +7669,10 @@
         <v>1.42</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8489</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>17.8269</v>
+        <v>17.8353</v>
       </c>
     </row>
     <row r="88">
@@ -7706,13 +7706,13 @@
         <v>21</v>
       </c>
       <c r="H88" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7332</v>
+        <v>0.7188</v>
       </c>
       <c r="J88" t="n">
-        <v>15.3972</v>
+        <v>15.0948</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>1.15</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4336</v>
+        <v>0.4338</v>
       </c>
       <c r="J89" t="n">
-        <v>9.105600000000001</v>
+        <v>9.1098</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>1.15</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4336</v>
+        <v>0.4338</v>
       </c>
       <c r="J90" t="n">
-        <v>9.105600000000001</v>
+        <v>9.1098</v>
       </c>
     </row>
     <row r="91">
@@ -7829,16 +7829,16 @@
         <v>0.85</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5041</v>
+        <v>-0.5037</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.5861</v>
+        <v>-10.5777</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7866,19 +7866,19 @@
         <v>18</v>
       </c>
       <c r="H92" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.1576</v>
+        <v>-0.1466</v>
       </c>
       <c r="J92" t="n">
-        <v>-2.8368</v>
+        <v>-2.6388</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7909,10 +7909,10 @@
         <v>0.87</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1576</v>
+        <v>-0.1579</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.8368</v>
+        <v>-2.8422</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>0.86</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1686</v>
+        <v>-0.1689</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.0348</v>
+        <v>-3.0402</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>0.78</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2502</v>
+        <v>-0.2504</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.5036</v>
+        <v>-4.5072</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.42</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5703</v>
+        <v>-0.5705</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.2654</v>
+        <v>-10.269</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.59</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0407</v>
+        <v>1.041</v>
       </c>
       <c r="J97" t="n">
-        <v>18.7326</v>
+        <v>18.738</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>1.42</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8186</v>
+        <v>0.8187</v>
       </c>
       <c r="J98" t="n">
-        <v>14.7348</v>
+        <v>14.7366</v>
       </c>
     </row>
     <row r="99">
@@ -8146,13 +8146,13 @@
         <v>18</v>
       </c>
       <c r="H99" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="I99" t="n">
-        <v>0.724</v>
+        <v>0.7101</v>
       </c>
       <c r="J99" t="n">
-        <v>13.032</v>
+        <v>12.7818</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>1.32</v>
       </c>
       <c r="I100" t="n">
-        <v>0.6813</v>
+        <v>0.6815</v>
       </c>
       <c r="J100" t="n">
-        <v>12.2634</v>
+        <v>12.267</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>1.32</v>
       </c>
       <c r="I101" t="n">
-        <v>0.6813</v>
+        <v>0.6815</v>
       </c>
       <c r="J101" t="n">
-        <v>12.2634</v>
+        <v>12.267</v>
       </c>
     </row>
     <row r="102">
@@ -8669,10 +8669,10 @@
         <v>1.08</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3041</v>
+        <v>0.3031</v>
       </c>
       <c r="J112" t="n">
-        <v>4.8656</v>
+        <v>4.8496</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>0.78</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2448</v>
+        <v>-0.245</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.9168</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>0.6</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4076</v>
+        <v>-0.4078</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.5216</v>
+        <v>-6.5248</v>
       </c>
     </row>
     <row r="115">
@@ -8786,13 +8786,13 @@
         <v>16</v>
       </c>
       <c r="H115" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4165</v>
+        <v>-0.4078</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.664</v>
+        <v>-6.5248</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.52</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4783</v>
+        <v>-0.4785</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.6528</v>
+        <v>-7.656</v>
       </c>
     </row>
     <row r="117">
@@ -9069,10 +9069,10 @@
         <v>1.1</v>
       </c>
       <c r="I122" t="n">
-        <v>0.263</v>
+        <v>0.2626</v>
       </c>
       <c r="J122" t="n">
-        <v>6.312</v>
+        <v>6.3024</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>0.98</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0398</v>
+        <v>-0.0399</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.9552</v>
+        <v>-0.9576</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>0.95</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0828</v>
+        <v>-0.0829</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.9872</v>
+        <v>-1.9896</v>
       </c>
     </row>
     <row r="125">
@@ -9186,13 +9186,13 @@
         <v>24</v>
       </c>
       <c r="H125" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0954</v>
+        <v>-0.0829</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.2896</v>
+        <v>-1.9896</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.77</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2769</v>
+        <v>-0.2771</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.6456</v>
+        <v>-6.6504</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.54</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0182</v>
+        <v>1.0187</v>
       </c>
       <c r="J127" t="n">
-        <v>24.4368</v>
+        <v>24.4488</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.18</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4872</v>
+        <v>0.4874</v>
       </c>
       <c r="J128" t="n">
-        <v>11.6928</v>
+        <v>11.6976</v>
       </c>
     </row>
     <row r="129">
@@ -9346,13 +9346,13 @@
         <v>24</v>
       </c>
       <c r="H129" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4538</v>
+        <v>0.4349</v>
       </c>
       <c r="J129" t="n">
-        <v>10.8912</v>
+        <v>10.4376</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>1.13</v>
       </c>
       <c r="I130" t="n">
-        <v>0.3899</v>
+        <v>0.3902</v>
       </c>
       <c r="J130" t="n">
-        <v>9.3576</v>
+        <v>9.364800000000001</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.85</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5023</v>
+        <v>-0.502</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.0552</v>
+        <v>-12.048</v>
       </c>
     </row>
     <row r="132">
@@ -10469,10 +10469,10 @@
         <v>1.29</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5742</v>
+        <v>0.573</v>
       </c>
       <c r="J157" t="n">
-        <v>9.7614</v>
+        <v>9.741</v>
       </c>
     </row>
     <row r="158">
@@ -10506,13 +10506,13 @@
         <v>17</v>
       </c>
       <c r="H158" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5372</v>
+        <v>0.5607</v>
       </c>
       <c r="J158" t="n">
-        <v>9.132400000000001</v>
+        <v>9.5319</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>0.73</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3082</v>
+        <v>-0.3086</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.2394</v>
+        <v>-5.2462</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>0.67</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3637</v>
+        <v>-0.3641</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.1829</v>
+        <v>-6.1897</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>0.45</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5558</v>
+        <v>-0.5561</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.448600000000001</v>
+        <v>-9.4537</v>
       </c>
     </row>
     <row r="162">
@@ -10666,13 +10666,13 @@
         <v>17</v>
       </c>
       <c r="H162" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="I162" t="n">
-        <v>1.7175</v>
+        <v>1.7066</v>
       </c>
       <c r="J162" t="n">
-        <v>29.1975</v>
+        <v>29.0122</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.69</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1531</v>
+        <v>1.1534</v>
       </c>
       <c r="J163" t="n">
-        <v>19.6027</v>
+        <v>19.6078</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>1.4</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7851</v>
+        <v>0.7852</v>
       </c>
       <c r="J164" t="n">
-        <v>13.3467</v>
+        <v>13.3484</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>1.29</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6278</v>
+        <v>0.628</v>
       </c>
       <c r="J165" t="n">
-        <v>10.6726</v>
+        <v>10.676</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.91</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3973</v>
+        <v>-0.397</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.7541</v>
+        <v>-6.749</v>
       </c>
     </row>
     <row r="167">
@@ -11869,10 +11869,10 @@
         <v>0.91</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.1095</v>
+        <v>-0.1091</v>
       </c>
       <c r="J192" t="n">
-        <v>-1.8615</v>
+        <v>-1.8547</v>
       </c>
     </row>
     <row r="193">
@@ -11906,13 +11906,13 @@
         <v>17</v>
       </c>
       <c r="H193" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1674</v>
+        <v>-0.1779</v>
       </c>
       <c r="J193" t="n">
-        <v>-2.8458</v>
+        <v>-3.0243</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.77</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2589</v>
+        <v>-0.2587</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.4013</v>
+        <v>-4.3979</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.63</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3855</v>
+        <v>-0.3853</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.5535</v>
+        <v>-6.5501</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.59</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4212</v>
+        <v>-0.4209</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.1604</v>
+        <v>-7.1553</v>
       </c>
     </row>
     <row r="197">
@@ -12869,10 +12869,10 @@
         <v>1.26</v>
       </c>
       <c r="I217" t="n">
-        <v>0.535</v>
+        <v>0.5344</v>
       </c>
       <c r="J217" t="n">
-        <v>12.84</v>
+        <v>12.8256</v>
       </c>
     </row>
     <row r="218">
@@ -12906,13 +12906,13 @@
         <v>24</v>
       </c>
       <c r="H218" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2134</v>
+        <v>0.2334</v>
       </c>
       <c r="J218" t="n">
-        <v>5.1216</v>
+        <v>5.6016</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.04</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1254</v>
+        <v>0.1251</v>
       </c>
       <c r="J219" t="n">
-        <v>3.0096</v>
+        <v>3.0024</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.84</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2114</v>
+        <v>-0.2115</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.0736</v>
+        <v>-5.076</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.75</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3004</v>
+        <v>-0.3006</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.2096</v>
+        <v>-7.2144</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.61</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2697</v>
+        <v>1.2692</v>
       </c>
       <c r="J222" t="n">
-        <v>30.4728</v>
+        <v>30.4608</v>
       </c>
     </row>
     <row r="223">
@@ -13106,13 +13106,13 @@
         <v>24</v>
       </c>
       <c r="H223" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0766</v>
+        <v>1.0903</v>
       </c>
       <c r="J223" t="n">
-        <v>25.8384</v>
+        <v>26.1672</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2565</v>
+        <v>-0.2569</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.156</v>
+        <v>-6.1656</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>0.86</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4716</v>
+        <v>-0.4719</v>
       </c>
       <c r="J225" t="n">
-        <v>-11.3184</v>
+        <v>-11.3256</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5914</v>
+        <v>-0.5918</v>
       </c>
       <c r="J226" t="n">
-        <v>-14.1936</v>
+        <v>-14.2032</v>
       </c>
     </row>
     <row r="227">
@@ -14669,10 +14669,10 @@
         <v>1.29</v>
       </c>
       <c r="I262" t="n">
-        <v>0.6365</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="J262" t="n">
-        <v>12.0935</v>
+        <v>12.0764</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>0.97</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0442</v>
+        <v>-0.0445</v>
       </c>
       <c r="J263" t="n">
-        <v>-0.8398</v>
+        <v>-0.8455</v>
       </c>
     </row>
     <row r="264">
@@ -14746,13 +14746,13 @@
         <v>19</v>
       </c>
       <c r="H264" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2084</v>
+        <v>-0.1986</v>
       </c>
       <c r="J264" t="n">
-        <v>-3.9596</v>
+        <v>-3.7734</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>0.59</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4318</v>
+        <v>-0.432</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.2042</v>
+        <v>-8.208</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>0.55</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4669</v>
+        <v>-0.4671</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.8711</v>
+        <v>-8.8749</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>1.57</v>
       </c>
       <c r="I267" t="n">
-        <v>1.181</v>
+        <v>1.1814</v>
       </c>
       <c r="J267" t="n">
-        <v>22.439</v>
+        <v>22.4466</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>1.52</v>
       </c>
       <c r="I268" t="n">
-        <v>1.1146</v>
+        <v>1.1149</v>
       </c>
       <c r="J268" t="n">
-        <v>21.1774</v>
+        <v>21.1831</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>1.22</v>
       </c>
       <c r="I269" t="n">
-        <v>0.578</v>
+        <v>0.5782</v>
       </c>
       <c r="J269" t="n">
-        <v>10.982</v>
+        <v>10.9858</v>
       </c>
     </row>
     <row r="270">
@@ -14986,13 +14986,13 @@
         <v>19</v>
       </c>
       <c r="H270" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="I270" t="n">
-        <v>0.5564</v>
+        <v>0.5349</v>
       </c>
       <c r="J270" t="n">
-        <v>10.5716</v>
+        <v>10.1631</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.91</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3676</v>
+        <v>-0.3673</v>
       </c>
       <c r="J271" t="n">
-        <v>-6.9844</v>
+        <v>-6.9787</v>
       </c>
     </row>
     <row r="272">
@@ -16469,10 +16469,10 @@
         <v>1.2</v>
       </c>
       <c r="I307" t="n">
-        <v>0.5019</v>
+        <v>0.501</v>
       </c>
       <c r="J307" t="n">
-        <v>9.536099999999999</v>
+        <v>9.519</v>
       </c>
     </row>
     <row r="308">
@@ -16509,16 +16509,16 @@
         <v>0.9</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.129</v>
+        <v>-0.1293</v>
       </c>
       <c r="J308" t="n">
-        <v>-2.451</v>
+        <v>-2.4567</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -16549,16 +16549,16 @@
         <v>0.76</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2716</v>
+        <v>-0.2718</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.1604</v>
+        <v>-5.1642</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -16586,13 +16586,13 @@
         <v>19</v>
       </c>
       <c r="H310" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.281</v>
+        <v>-0.2718</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.339</v>
+        <v>-5.1642</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>0.38</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6079</v>
+        <v>-0.608</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.5501</v>
+        <v>-11.552</v>
       </c>
     </row>
     <row r="312">
@@ -17066,13 +17066,13 @@
         <v>21</v>
       </c>
       <c r="H322" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="I322" t="n">
-        <v>1.4942</v>
+        <v>1.4822</v>
       </c>
       <c r="J322" t="n">
-        <v>31.3782</v>
+        <v>31.1262</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.7</v>
       </c>
       <c r="I323" t="n">
-        <v>1.3547</v>
+        <v>1.3552</v>
       </c>
       <c r="J323" t="n">
-        <v>28.4487</v>
+        <v>28.4592</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>1.08</v>
       </c>
       <c r="I324" t="n">
-        <v>0.246</v>
+        <v>0.2463</v>
       </c>
       <c r="J324" t="n">
-        <v>5.166</v>
+        <v>5.1723</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>0.96</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2164</v>
+        <v>-0.216</v>
       </c>
       <c r="J325" t="n">
-        <v>-4.5444</v>
+        <v>-4.536</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.77</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.7033</v>
+        <v>-0.703</v>
       </c>
       <c r="J326" t="n">
-        <v>-14.7693</v>
+        <v>-14.763</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.6</v>
       </c>
       <c r="I327" t="n">
-        <v>1.0248</v>
+        <v>1.0242</v>
       </c>
       <c r="J327" t="n">
-        <v>21.5208</v>
+        <v>21.5082</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>1.15</v>
       </c>
       <c r="I328" t="n">
-        <v>0.3437</v>
+        <v>0.3433</v>
       </c>
       <c r="J328" t="n">
-        <v>7.2177</v>
+        <v>7.2093</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>0.98</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0435</v>
+        <v>-0.0436</v>
       </c>
       <c r="J329" t="n">
-        <v>-0.9135</v>
+        <v>-0.9156</v>
       </c>
     </row>
     <row r="330">
@@ -17386,13 +17386,13 @@
         <v>21</v>
       </c>
       <c r="H330" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1</v>
+        <v>-0.0871</v>
       </c>
       <c r="J330" t="n">
-        <v>-2.1</v>
+        <v>-1.8291</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.39</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6147</v>
+        <v>-0.6148</v>
       </c>
       <c r="J331" t="n">
-        <v>-12.9087</v>
+        <v>-12.9108</v>
       </c>
     </row>
     <row r="332">
@@ -17666,13 +17666,13 @@
         <v>23</v>
       </c>
       <c r="H337" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3256</v>
+        <v>0.3439</v>
       </c>
       <c r="J337" t="n">
-        <v>7.4888</v>
+        <v>7.9097</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>0.96</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.0683</v>
+        <v>-0.0684</v>
       </c>
       <c r="J338" t="n">
-        <v>-1.5709</v>
+        <v>-1.5732</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>0.91</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1299</v>
+        <v>-0.13</v>
       </c>
       <c r="J339" t="n">
-        <v>-2.9877</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.87</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.174</v>
+        <v>-0.1742</v>
       </c>
       <c r="J340" t="n">
-        <v>-4.002</v>
+        <v>-4.0066</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.78</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2655</v>
+        <v>-0.2657</v>
       </c>
       <c r="J341" t="n">
-        <v>-6.1065</v>
+        <v>-6.1111</v>
       </c>
     </row>
     <row r="342">
@@ -20269,10 +20269,10 @@
         <v>1.25</v>
       </c>
       <c r="I402" t="n">
-        <v>0.3744</v>
+        <v>0.3741</v>
       </c>
       <c r="J402" t="n">
-        <v>10.4832</v>
+        <v>10.4748</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.25</v>
       </c>
       <c r="I403" t="n">
-        <v>0.3744</v>
+        <v>0.3741</v>
       </c>
       <c r="J403" t="n">
-        <v>10.4832</v>
+        <v>10.4748</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>1.16</v>
       </c>
       <c r="I404" t="n">
-        <v>0.2626</v>
+        <v>0.2623</v>
       </c>
       <c r="J404" t="n">
-        <v>7.3528</v>
+        <v>7.3444</v>
       </c>
     </row>
     <row r="405">
@@ -20386,13 +20386,13 @@
         <v>28</v>
       </c>
       <c r="H405" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.1517</v>
+        <v>-0.1403</v>
       </c>
       <c r="J405" t="n">
-        <v>-4.2476</v>
+        <v>-3.9284</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.72</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.334</v>
+        <v>-0.3341</v>
       </c>
       <c r="J406" t="n">
-        <v>-9.352</v>
+        <v>-9.354799999999999</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>1.37</v>
       </c>
       <c r="I407" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.5524</v>
       </c>
       <c r="J407" t="n">
-        <v>15.4812</v>
+        <v>15.4672</v>
       </c>
     </row>
     <row r="408">
@@ -20506,13 +20506,13 @@
         <v>28</v>
       </c>
       <c r="H408" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I408" t="n">
-        <v>0.1158</v>
+        <v>0.133</v>
       </c>
       <c r="J408" t="n">
-        <v>3.2424</v>
+        <v>3.724</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>0.9</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.1469</v>
+        <v>-0.1471</v>
       </c>
       <c r="J409" t="n">
-        <v>-4.1132</v>
+        <v>-4.1188</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>0.89</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.1582</v>
+        <v>-0.1584</v>
       </c>
       <c r="J410" t="n">
-        <v>-4.4296</v>
+        <v>-4.4352</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>0.79</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.2623</v>
+        <v>-0.2625</v>
       </c>
       <c r="J411" t="n">
-        <v>-7.3444</v>
+        <v>-7.35</v>
       </c>
     </row>
     <row r="412">
@@ -20666,13 +20666,13 @@
         <v>21</v>
       </c>
       <c r="H412" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="I412" t="n">
-        <v>1.0484</v>
+        <v>1.0372</v>
       </c>
       <c r="J412" t="n">
-        <v>22.0164</v>
+        <v>21.7812</v>
       </c>
     </row>
     <row r="413">
@@ -20826,13 +20826,13 @@
         <v>21</v>
       </c>
       <c r="H416" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.4613</v>
+        <v>-0.4527</v>
       </c>
       <c r="J416" t="n">
-        <v>-9.6873</v>
+        <v>-9.5067</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>1.54</v>
       </c>
       <c r="I417" t="n">
-        <v>1.1518</v>
+        <v>1.1514</v>
       </c>
       <c r="J417" t="n">
-        <v>24.1878</v>
+        <v>24.1794</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>1.53</v>
       </c>
       <c r="I418" t="n">
-        <v>1.1383</v>
+        <v>1.1379</v>
       </c>
       <c r="J418" t="n">
-        <v>23.9043</v>
+        <v>23.8959</v>
       </c>
     </row>
     <row r="419">
@@ -20946,13 +20946,13 @@
         <v>21</v>
       </c>
       <c r="H419" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="I419" t="n">
-        <v>0.7071</v>
+        <v>0.7269</v>
       </c>
       <c r="J419" t="n">
-        <v>14.8491</v>
+        <v>15.2649</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.99</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.099</v>
+        <v>-0.0993</v>
       </c>
       <c r="J420" t="n">
-        <v>-2.079</v>
+        <v>-2.0853</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>0.82</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.5843</v>
+        <v>-0.5846</v>
       </c>
       <c r="J421" t="n">
-        <v>-12.2703</v>
+        <v>-12.2766</v>
       </c>
     </row>
     <row r="422">
@@ -22069,10 +22069,10 @@
         <v>1.13</v>
       </c>
       <c r="I447" t="n">
-        <v>0.2478</v>
+        <v>0.2475</v>
       </c>
       <c r="J447" t="n">
-        <v>5.6994</v>
+        <v>5.6925</v>
       </c>
     </row>
     <row r="448">
@@ -22109,10 +22109,10 @@
         <v>1.1</v>
       </c>
       <c r="I448" t="n">
-        <v>0.2026</v>
+        <v>0.2023</v>
       </c>
       <c r="J448" t="n">
-        <v>4.6598</v>
+        <v>4.6529</v>
       </c>
     </row>
     <row r="449">
@@ -22149,10 +22149,10 @@
         <v>1.01</v>
       </c>
       <c r="I449" t="n">
-        <v>0.037</v>
+        <v>0.0367</v>
       </c>
       <c r="J449" t="n">
-        <v>0.851</v>
+        <v>0.8441</v>
       </c>
     </row>
     <row r="450">
@@ -22189,10 +22189,10 @@
         <v>0.99</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.0236</v>
+        <v>-0.0238</v>
       </c>
       <c r="J450" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.5474</v>
       </c>
     </row>
     <row r="451">
@@ -22226,13 +22226,13 @@
         <v>23</v>
       </c>
       <c r="H451" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.4257</v>
+        <v>-0.4171</v>
       </c>
       <c r="J451" t="n">
-        <v>-9.7911</v>
+        <v>-9.593299999999999</v>
       </c>
     </row>
     <row r="452">
@@ -22269,10 +22269,10 @@
         <v>1.09</v>
       </c>
       <c r="I452" t="n">
-        <v>0.2525</v>
+        <v>0.252</v>
       </c>
       <c r="J452" t="n">
-        <v>6.06</v>
+        <v>6.048</v>
       </c>
     </row>
     <row r="453">
@@ -22309,10 +22309,10 @@
         <v>0.9</v>
       </c>
       <c r="I453" t="n">
-        <v>-0.1397</v>
+        <v>-0.1398</v>
       </c>
       <c r="J453" t="n">
-        <v>-3.3528</v>
+        <v>-3.3552</v>
       </c>
     </row>
     <row r="454">
@@ -22349,10 +22349,10 @@
         <v>0.9</v>
       </c>
       <c r="I454" t="n">
-        <v>-0.1397</v>
+        <v>-0.1398</v>
       </c>
       <c r="J454" t="n">
-        <v>-3.3528</v>
+        <v>-3.3552</v>
       </c>
     </row>
     <row r="455">
@@ -22386,13 +22386,13 @@
         <v>24</v>
       </c>
       <c r="H455" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="I455" t="n">
-        <v>-0.1827</v>
+        <v>-0.1723</v>
       </c>
       <c r="J455" t="n">
-        <v>-4.3848</v>
+        <v>-4.1352</v>
       </c>
     </row>
     <row r="456">
@@ -22429,10 +22429,10 @@
         <v>0.79</v>
       </c>
       <c r="I456" t="n">
-        <v>-0.2536</v>
+        <v>-0.2538</v>
       </c>
       <c r="J456" t="n">
-        <v>-6.0864</v>
+        <v>-6.0912</v>
       </c>
     </row>
     <row r="457">
@@ -22469,10 +22469,10 @@
         <v>1.51</v>
       </c>
       <c r="I457" t="n">
-        <v>1.1466</v>
+        <v>1.1472</v>
       </c>
       <c r="J457" t="n">
-        <v>27.5184</v>
+        <v>27.5328</v>
       </c>
     </row>
     <row r="458">
@@ -22509,10 +22509,10 @@
         <v>1.15</v>
       </c>
       <c r="I458" t="n">
-        <v>0.4482</v>
+        <v>0.4486</v>
       </c>
       <c r="J458" t="n">
-        <v>10.7568</v>
+        <v>10.7664</v>
       </c>
     </row>
     <row r="459">
@@ -22546,13 +22546,13 @@
         <v>24</v>
       </c>
       <c r="H459" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="I459" t="n">
-        <v>-0.0135</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="J459" t="n">
-        <v>-0.324</v>
+        <v>-1.7496</v>
       </c>
     </row>
     <row r="460">
@@ -22589,10 +22589,10 @@
         <v>0.92</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.3048</v>
+        <v>-0.3044</v>
       </c>
       <c r="J460" t="n">
-        <v>-7.3152</v>
+        <v>-7.3056</v>
       </c>
     </row>
     <row r="461">
@@ -22629,10 +22629,10 @@
         <v>0.86</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.4621</v>
+        <v>-0.4617</v>
       </c>
       <c r="J461" t="n">
-        <v>-11.0904</v>
+        <v>-11.0808</v>
       </c>
     </row>
     <row r="462">
@@ -23069,10 +23069,10 @@
         <v>1.62</v>
       </c>
       <c r="I472" t="n">
-        <v>1.2677</v>
+        <v>1.2682</v>
       </c>
       <c r="J472" t="n">
-        <v>29.1571</v>
+        <v>29.1686</v>
       </c>
     </row>
     <row r="473">
@@ -23109,10 +23109,10 @@
         <v>1.57</v>
       </c>
       <c r="I473" t="n">
-        <v>1.2008</v>
+        <v>1.2013</v>
       </c>
       <c r="J473" t="n">
-        <v>27.6184</v>
+        <v>27.6299</v>
       </c>
     </row>
     <row r="474">
@@ -23146,13 +23146,13 @@
         <v>23</v>
       </c>
       <c r="H474" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="I474" t="n">
-        <v>0.7134</v>
+        <v>0.6932</v>
       </c>
       <c r="J474" t="n">
-        <v>16.4082</v>
+        <v>15.9436</v>
       </c>
     </row>
     <row r="475">
@@ -23189,10 +23189,10 @@
         <v>0.78</v>
       </c>
       <c r="I475" t="n">
-        <v>-0.6698</v>
+        <v>-0.6695</v>
       </c>
       <c r="J475" t="n">
-        <v>-15.4054</v>
+        <v>-15.3985</v>
       </c>
     </row>
     <row r="476">
@@ -23229,10 +23229,10 @@
         <v>0.72</v>
       </c>
       <c r="I476" t="n">
-        <v>-0.8014</v>
+        <v>-0.8011</v>
       </c>
       <c r="J476" t="n">
-        <v>-18.4322</v>
+        <v>-18.4253</v>
       </c>
     </row>
     <row r="477">
@@ -23269,10 +23269,10 @@
         <v>1.44</v>
       </c>
       <c r="I477" t="n">
-        <v>0.8054</v>
+        <v>0.8048</v>
       </c>
       <c r="J477" t="n">
-        <v>18.5242</v>
+        <v>18.5104</v>
       </c>
     </row>
     <row r="478">
@@ -23306,13 +23306,13 @@
         <v>23</v>
       </c>
       <c r="H478" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="I478" t="n">
-        <v>-0.0593</v>
+        <v>-0.0439</v>
       </c>
       <c r="J478" t="n">
-        <v>-1.3639</v>
+        <v>-1.0097</v>
       </c>
     </row>
     <row r="479">
@@ -23349,10 +23349,10 @@
         <v>0.97</v>
       </c>
       <c r="I479" t="n">
-        <v>-0.0593</v>
+        <v>-0.0595</v>
       </c>
       <c r="J479" t="n">
-        <v>-1.3639</v>
+        <v>-1.3685</v>
       </c>
     </row>
     <row r="480">
@@ -23389,10 +23389,10 @@
         <v>0.91</v>
       </c>
       <c r="I480" t="n">
-        <v>-0.1368</v>
+        <v>-0.1369</v>
       </c>
       <c r="J480" t="n">
-        <v>-3.1464</v>
+        <v>-3.1487</v>
       </c>
     </row>
     <row r="481">
@@ -23429,10 +23429,10 @@
         <v>0.79</v>
       </c>
       <c r="I481" t="n">
-        <v>-0.2637</v>
+        <v>-0.2639</v>
       </c>
       <c r="J481" t="n">
-        <v>-6.0651</v>
+        <v>-6.0697</v>
       </c>
     </row>
     <row r="482">
@@ -23869,10 +23869,10 @@
         <v>1.05</v>
       </c>
       <c r="I492" t="n">
-        <v>0.2613</v>
+        <v>0.2601</v>
       </c>
       <c r="J492" t="n">
-        <v>3.6582</v>
+        <v>3.6414</v>
       </c>
     </row>
     <row r="493">
@@ -23909,10 +23909,10 @@
         <v>0.74</v>
       </c>
       <c r="I493" t="n">
-        <v>-0.2762</v>
+        <v>-0.2765</v>
       </c>
       <c r="J493" t="n">
-        <v>-3.8668</v>
+        <v>-3.871</v>
       </c>
     </row>
     <row r="494">
@@ -23949,10 +23949,10 @@
         <v>0.7</v>
       </c>
       <c r="I494" t="n">
-        <v>-0.314</v>
+        <v>-0.3142</v>
       </c>
       <c r="J494" t="n">
-        <v>-4.396</v>
+        <v>-4.3988</v>
       </c>
     </row>
     <row r="495">
@@ -23986,13 +23986,13 @@
         <v>14</v>
       </c>
       <c r="H495" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="I495" t="n">
-        <v>-0.4893</v>
+        <v>-0.4808</v>
       </c>
       <c r="J495" t="n">
-        <v>-6.8502</v>
+        <v>-6.7312</v>
       </c>
     </row>
     <row r="496">
@@ -24029,10 +24029,10 @@
         <v>0.33</v>
       </c>
       <c r="I496" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6378</v>
       </c>
       <c r="J496" t="n">
-        <v>-8.926399999999999</v>
+        <v>-8.9292</v>
       </c>
     </row>
     <row r="497">
@@ -24109,10 +24109,10 @@
         <v>1.76</v>
       </c>
       <c r="I498" t="n">
-        <v>1.3698</v>
+        <v>1.37</v>
       </c>
       <c r="J498" t="n">
-        <v>19.1772</v>
+        <v>19.18</v>
       </c>
     </row>
     <row r="499">
@@ -24146,13 +24146,13 @@
         <v>14</v>
       </c>
       <c r="H499" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I499" t="n">
-        <v>1.0669</v>
+        <v>1.0537</v>
       </c>
       <c r="J499" t="n">
-        <v>14.9366</v>
+        <v>14.7518</v>
       </c>
     </row>
     <row r="500">
@@ -24189,10 +24189,10 @@
         <v>1.33</v>
       </c>
       <c r="I500" t="n">
-        <v>0.7574</v>
+        <v>0.7577</v>
       </c>
       <c r="J500" t="n">
-        <v>10.6036</v>
+        <v>10.6078</v>
       </c>
     </row>
     <row r="501">
@@ -24229,10 +24229,10 @@
         <v>1.17</v>
       </c>
       <c r="I501" t="n">
-        <v>0.4195</v>
+        <v>0.4197</v>
       </c>
       <c r="J501" t="n">
-        <v>5.873</v>
+        <v>5.8758</v>
       </c>
     </row>
     <row r="502">
@@ -26866,13 +26866,13 @@
         <v>18</v>
       </c>
       <c r="H567" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="I567" t="n">
-        <v>1.5275</v>
+        <v>1.5158</v>
       </c>
       <c r="J567" t="n">
-        <v>27.495</v>
+        <v>27.2844</v>
       </c>
     </row>
     <row r="568">
@@ -26909,10 +26909,10 @@
         <v>1.74</v>
       </c>
       <c r="I568" t="n">
-        <v>1.3803</v>
+        <v>1.3807</v>
       </c>
       <c r="J568" t="n">
-        <v>24.8454</v>
+        <v>24.8526</v>
       </c>
     </row>
     <row r="569">
@@ -26949,10 +26949,10 @@
         <v>1.31</v>
       </c>
       <c r="I569" t="n">
-        <v>0.7498</v>
+        <v>0.75</v>
       </c>
       <c r="J569" t="n">
-        <v>13.4964</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="570">
@@ -26989,10 +26989,10 @@
         <v>1.1</v>
       </c>
       <c r="I570" t="n">
-        <v>0.2813</v>
+        <v>0.2816</v>
       </c>
       <c r="J570" t="n">
-        <v>5.0634</v>
+        <v>5.0688</v>
       </c>
     </row>
     <row r="571">
@@ -27029,10 +27029,10 @@
         <v>0.89</v>
       </c>
       <c r="I571" t="n">
-        <v>-0.435</v>
+        <v>-0.4348</v>
       </c>
       <c r="J571" t="n">
-        <v>-7.83</v>
+        <v>-7.8264</v>
       </c>
     </row>
     <row r="572">
@@ -27266,7 +27266,7 @@
         <v>18</v>
       </c>
       <c r="H577" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="I577" t="n">
         <v>1.9372</v>
@@ -27309,10 +27309,10 @@
         <v>1.31</v>
       </c>
       <c r="I578" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7447</v>
       </c>
       <c r="J578" t="n">
-        <v>13.401</v>
+        <v>13.4046</v>
       </c>
     </row>
     <row r="579">
@@ -27349,10 +27349,10 @@
         <v>1.29</v>
       </c>
       <c r="I579" t="n">
-        <v>0.7045</v>
+        <v>0.7048</v>
       </c>
       <c r="J579" t="n">
-        <v>12.681</v>
+        <v>12.6864</v>
       </c>
     </row>
     <row r="580">
@@ -27389,10 +27389,10 @@
         <v>1.25</v>
       </c>
       <c r="I580" t="n">
-        <v>0.6224</v>
+        <v>0.6226</v>
       </c>
       <c r="J580" t="n">
-        <v>11.2032</v>
+        <v>11.2068</v>
       </c>
     </row>
     <row r="581">
@@ -27429,10 +27429,10 @@
         <v>0.84</v>
       </c>
       <c r="I581" t="n">
-        <v>-0.5647</v>
+        <v>-0.5644</v>
       </c>
       <c r="J581" t="n">
-        <v>-10.1646</v>
+        <v>-10.1592</v>
       </c>
     </row>
     <row r="582">
@@ -27466,13 +27466,13 @@
         <v>17</v>
       </c>
       <c r="H582" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="I582" t="n">
-        <v>0.6587</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J582" t="n">
-        <v>11.1979</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="583">
@@ -27509,10 +27509,10 @@
         <v>1.1</v>
       </c>
       <c r="I583" t="n">
-        <v>0.2954</v>
+        <v>0.294</v>
       </c>
       <c r="J583" t="n">
-        <v>5.0218</v>
+        <v>4.998</v>
       </c>
     </row>
     <row r="584">
@@ -27549,10 +27549,10 @@
         <v>0.76</v>
       </c>
       <c r="I584" t="n">
-        <v>-0.2751</v>
+        <v>-0.2755</v>
       </c>
       <c r="J584" t="n">
-        <v>-4.6767</v>
+        <v>-4.6835</v>
       </c>
     </row>
     <row r="585">
@@ -27589,10 +27589,10 @@
         <v>0.71</v>
       </c>
       <c r="I585" t="n">
-        <v>-0.322</v>
+        <v>-0.3225</v>
       </c>
       <c r="J585" t="n">
-        <v>-5.474</v>
+        <v>-5.4825</v>
       </c>
     </row>
     <row r="586">
@@ -27629,10 +27629,10 @@
         <v>0.3</v>
       </c>
       <c r="I586" t="n">
-        <v>-0.6774</v>
+        <v>-0.6776</v>
       </c>
       <c r="J586" t="n">
-        <v>-11.5158</v>
+        <v>-11.5192</v>
       </c>
     </row>
     <row r="587">
@@ -27669,10 +27669,10 @@
         <v>1.91</v>
       </c>
       <c r="I587" t="n">
-        <v>1.5883</v>
+        <v>1.5888</v>
       </c>
       <c r="J587" t="n">
-        <v>27.0011</v>
+        <v>27.0096</v>
       </c>
     </row>
     <row r="588">
@@ -27709,10 +27709,10 @@
         <v>1.63</v>
       </c>
       <c r="I588" t="n">
-        <v>1.2424</v>
+        <v>1.2428</v>
       </c>
       <c r="J588" t="n">
-        <v>21.1208</v>
+        <v>21.1276</v>
       </c>
     </row>
     <row r="589">
@@ -27746,13 +27746,13 @@
         <v>17</v>
       </c>
       <c r="H589" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="I589" t="n">
-        <v>0.75</v>
+        <v>0.7305</v>
       </c>
       <c r="J589" t="n">
-        <v>12.75</v>
+        <v>12.4185</v>
       </c>
     </row>
     <row r="590">
@@ -27789,10 +27789,10 @@
         <v>1.16</v>
       </c>
       <c r="I590" t="n">
-        <v>0.4298</v>
+        <v>0.4301</v>
       </c>
       <c r="J590" t="n">
-        <v>7.3066</v>
+        <v>7.3117</v>
       </c>
     </row>
     <row r="591">
@@ -27829,10 +27829,10 @@
         <v>0.88</v>
       </c>
       <c r="I591" t="n">
-        <v>-0.4605</v>
+        <v>-0.4602</v>
       </c>
       <c r="J591" t="n">
-        <v>-7.8285</v>
+        <v>-7.8234</v>
       </c>
     </row>
     <row r="592">
@@ -27869,10 +27869,10 @@
         <v>1.19</v>
       </c>
       <c r="I592" t="n">
-        <v>0.4673</v>
+        <v>0.4665</v>
       </c>
       <c r="J592" t="n">
-        <v>9.346</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="593">
@@ -27909,16 +27909,16 @@
         <v>0.82</v>
       </c>
       <c r="I593" t="n">
-        <v>-0.2175</v>
+        <v>-0.2176</v>
       </c>
       <c r="J593" t="n">
-        <v>-4.35</v>
+        <v>-4.352</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -27949,16 +27949,16 @@
         <v>0.77</v>
       </c>
       <c r="I594" t="n">
-        <v>-0.2658</v>
+        <v>-0.266</v>
       </c>
       <c r="J594" t="n">
-        <v>-5.316</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -27986,13 +27986,13 @@
         <v>20</v>
       </c>
       <c r="H595" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="I595" t="n">
-        <v>-0.2753</v>
+        <v>-0.266</v>
       </c>
       <c r="J595" t="n">
-        <v>-5.506</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="596">
@@ -28029,10 +28029,10 @@
         <v>0.64</v>
       </c>
       <c r="I596" t="n">
-        <v>-0.3861</v>
+        <v>-0.3864</v>
       </c>
       <c r="J596" t="n">
-        <v>-7.722</v>
+        <v>-7.728</v>
       </c>
     </row>
     <row r="597">
